--- a/VerveStacks_IND/vt_vervestacks_IND_v1.xlsx
+++ b/VerveStacks_IND/vt_vervestacks_IND_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9E029A1-3166-47F3-AC53-94B672083EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17E290FC-90D4-4589-9863-6298F4DA6D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7F1C23D8-7B26-4A91-B9F5-5DB506DF35DD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AD837019-BA3B-4970-A13D-4AC5A4E1A3C5}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -6458,7 +6458,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE4E3214-D9D2-46D0-B415-EE4B49322BD1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DDC50E5-D8BC-4FE6-9A73-B7DCE3007961}">
   <dimension ref="B9:T414"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27161,7 +27161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A47604AC-CDA9-4446-9875-548609E8C7C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F79F193-2D5B-4C81-8709-758E313C9C22}">
   <dimension ref="B9:T905"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_IND/vt_vervestacks_IND_v1.xlsx
+++ b/VerveStacks_IND/vt_vervestacks_IND_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17E290FC-90D4-4589-9863-6298F4DA6D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B96B5F5-0852-4278-B17F-9F14C963C0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AD837019-BA3B-4970-A13D-4AC5A4E1A3C5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{86AD4835-1340-4176-9DE7-134A2D4299FF}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -6458,7 +6458,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DDC50E5-D8BC-4FE6-9A73-B7DCE3007961}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AD6908D-B7C2-4745-91B2-E24B92D37643}">
   <dimension ref="B9:T414"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27161,7 +27161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F79F193-2D5B-4C81-8709-758E313C9C22}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E834264-62CB-47E6-9DD0-88B9B895A8D8}">
   <dimension ref="B9:T905"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_IND/vt_vervestacks_IND_v1.xlsx
+++ b/VerveStacks_IND/vt_vervestacks_IND_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B96B5F5-0852-4278-B17F-9F14C963C0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{638F85AD-4658-4F6B-962D-73B424284113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{86AD4835-1340-4176-9DE7-134A2D4299FF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F3ACBFA8-769F-4790-8C8F-4AC11BCE07E9}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -6458,7 +6458,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AD6908D-B7C2-4745-91B2-E24B92D37643}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{489C10D1-C792-4265-9702-03CA55A14E91}">
   <dimension ref="B9:T414"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27161,7 +27161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E834264-62CB-47E6-9DD0-88B9B895A8D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BB859CB-57C7-44BE-AF28-AEF51B8BADA6}">
   <dimension ref="B9:T905"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -61287,7 +61287,7 @@
         <v>33</v>
       </c>
       <c r="L653">
-        <v>0.23343939125216409</v>
+        <v>0.23343939125216406</v>
       </c>
       <c r="N653" t="s">
         <v>723</v>

--- a/VerveStacks_IND/vt_vervestacks_IND_v1.xlsx
+++ b/VerveStacks_IND/vt_vervestacks_IND_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{638F85AD-4658-4F6B-962D-73B424284113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4F05878-C9DB-403A-BF76-993B04E4D29D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F3ACBFA8-769F-4790-8C8F-4AC11BCE07E9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B542A4B1-DAAE-4654-AEDD-7EF5E04B8492}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -6458,7 +6458,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{489C10D1-C792-4265-9702-03CA55A14E91}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21DC81A9-30E3-411F-88D5-CD314EA12529}">
   <dimension ref="B9:T414"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27161,7 +27161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BB859CB-57C7-44BE-AF28-AEF51B8BADA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{544B47F1-1D70-43DF-B8AA-F0D183D42046}">
   <dimension ref="B9:T905"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -61287,7 +61287,7 @@
         <v>33</v>
       </c>
       <c r="L653">
-        <v>0.23343939125216406</v>
+        <v>0.23343939125216409</v>
       </c>
       <c r="N653" t="s">
         <v>723</v>

--- a/VerveStacks_IND/vt_vervestacks_IND_v1.xlsx
+++ b/VerveStacks_IND/vt_vervestacks_IND_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4F05878-C9DB-403A-BF76-993B04E4D29D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{73C8E89E-71B5-4D1B-B515-4EC4429434F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B542A4B1-DAAE-4654-AEDD-7EF5E04B8492}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C3F88FAF-1EB9-48D3-83D3-E31C948607D1}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -6458,7 +6458,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21DC81A9-30E3-411F-88D5-CD314EA12529}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA1A9257-0EF1-4AF3-8856-4D8ADABE481E}">
   <dimension ref="B9:T414"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6537,7 +6537,7 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>0.10360320000000002</v>
+        <v>0.10671129600000002</v>
       </c>
       <c r="F11">
         <v>3583</v>
@@ -6593,7 +6593,7 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>0.10652160000000002</v>
+        <v>0.10971724800000002</v>
       </c>
       <c r="F12">
         <v>3583</v>
@@ -6649,7 +6649,7 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>0.10652160000000002</v>
+        <v>0.10971724800000002</v>
       </c>
       <c r="F13">
         <v>3583</v>
@@ -6705,7 +6705,7 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>0.10652160000000002</v>
+        <v>0.10971724800000002</v>
       </c>
       <c r="F14">
         <v>3583</v>
@@ -6761,7 +6761,7 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>0.10652160000000002</v>
+        <v>0.10971724800000002</v>
       </c>
       <c r="F15">
         <v>3583</v>
@@ -6817,7 +6817,7 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>0.10652160000000002</v>
+        <v>0.10971724800000002</v>
       </c>
       <c r="F16">
         <v>3583</v>
@@ -6873,7 +6873,7 @@
         <v>14</v>
       </c>
       <c r="E17">
-        <v>0.10652160000000002</v>
+        <v>0.10971724800000002</v>
       </c>
       <c r="F17">
         <v>3583</v>
@@ -6929,7 +6929,7 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>0.10652160000000002</v>
+        <v>0.10971724800000002</v>
       </c>
       <c r="F18">
         <v>3583</v>
@@ -6985,7 +6985,7 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>0.10652160000000002</v>
+        <v>0.10971724800000002</v>
       </c>
       <c r="F19">
         <v>3583</v>
@@ -7041,7 +7041,7 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F20">
         <v>1967</v>
@@ -7097,7 +7097,7 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F21">
         <v>1967</v>
@@ -7153,7 +7153,7 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F22">
         <v>1967</v>
@@ -7209,7 +7209,7 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F23">
         <v>1967</v>
@@ -7265,7 +7265,7 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F24">
         <v>1967</v>
@@ -7321,7 +7321,7 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F25">
         <v>1967</v>
@@ -7377,7 +7377,7 @@
         <v>14</v>
       </c>
       <c r="E26">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F26">
         <v>1967</v>
@@ -7433,7 +7433,7 @@
         <v>14</v>
       </c>
       <c r="E27">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F27">
         <v>1967</v>
@@ -7489,7 +7489,7 @@
         <v>14</v>
       </c>
       <c r="E28">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F28">
         <v>1967</v>
@@ -7545,7 +7545,7 @@
         <v>14</v>
       </c>
       <c r="E29">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F29">
         <v>1967</v>
@@ -7601,7 +7601,7 @@
         <v>14</v>
       </c>
       <c r="E30">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F30">
         <v>1967</v>
@@ -7657,7 +7657,7 @@
         <v>14</v>
       </c>
       <c r="E31">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F31">
         <v>1967</v>
@@ -7713,7 +7713,7 @@
         <v>14</v>
       </c>
       <c r="E32">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F32">
         <v>1967</v>
@@ -7769,7 +7769,7 @@
         <v>14</v>
       </c>
       <c r="E33">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F33">
         <v>1967</v>
@@ -7825,7 +7825,7 @@
         <v>14</v>
       </c>
       <c r="E34">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F34">
         <v>1967</v>
@@ -7881,7 +7881,7 @@
         <v>14</v>
       </c>
       <c r="E35">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F35">
         <v>1967</v>
@@ -7937,7 +7937,7 @@
         <v>14</v>
       </c>
       <c r="E36">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F36">
         <v>1967</v>
@@ -7993,7 +7993,7 @@
         <v>14</v>
       </c>
       <c r="E37">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F37">
         <v>1967</v>
@@ -8049,7 +8049,7 @@
         <v>14</v>
       </c>
       <c r="E38">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F38">
         <v>1967</v>
@@ -8105,7 +8105,7 @@
         <v>14</v>
       </c>
       <c r="E39">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F39">
         <v>1967</v>
@@ -8161,7 +8161,7 @@
         <v>14</v>
       </c>
       <c r="E40">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F40">
         <v>1967</v>
@@ -8217,7 +8217,7 @@
         <v>14</v>
       </c>
       <c r="E41">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F41">
         <v>1967</v>
@@ -8273,7 +8273,7 @@
         <v>14</v>
       </c>
       <c r="E42">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F42">
         <v>1967</v>
@@ -8329,7 +8329,7 @@
         <v>14</v>
       </c>
       <c r="E43">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F43">
         <v>1967</v>
@@ -8385,7 +8385,7 @@
         <v>14</v>
       </c>
       <c r="E44">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F44">
         <v>1967</v>
@@ -8441,7 +8441,7 @@
         <v>14</v>
       </c>
       <c r="E45">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F45">
         <v>1967</v>
@@ -8497,7 +8497,7 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F46">
         <v>1967</v>
@@ -8553,7 +8553,7 @@
         <v>14</v>
       </c>
       <c r="E47">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F47">
         <v>1967</v>
@@ -8609,7 +8609,7 @@
         <v>14</v>
       </c>
       <c r="E48">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F48">
         <v>1967</v>
@@ -8665,7 +8665,7 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F49">
         <v>1967</v>
@@ -8721,7 +8721,7 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>0.29203199999999996</v>
+        <v>0.30079295999999994</v>
       </c>
       <c r="F50">
         <v>1726</v>
@@ -8777,7 +8777,7 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <v>0.29203199999999996</v>
+        <v>0.30079295999999994</v>
       </c>
       <c r="F51">
         <v>1726</v>
@@ -8833,7 +8833,7 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F52">
         <v>1967</v>
@@ -8889,7 +8889,7 @@
         <v>14</v>
       </c>
       <c r="E53">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F53">
         <v>1967</v>
@@ -8945,7 +8945,7 @@
         <v>14</v>
       </c>
       <c r="E54">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F54">
         <v>1967</v>
@@ -9001,7 +9001,7 @@
         <v>14</v>
       </c>
       <c r="E55">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F55">
         <v>1967</v>
@@ -9057,7 +9057,7 @@
         <v>14</v>
       </c>
       <c r="E56">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F56">
         <v>1967</v>
@@ -9113,7 +9113,7 @@
         <v>14</v>
       </c>
       <c r="E57">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F57">
         <v>1967</v>
@@ -9169,7 +9169,7 @@
         <v>14</v>
       </c>
       <c r="E58">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F58">
         <v>1967</v>
@@ -9225,7 +9225,7 @@
         <v>14</v>
       </c>
       <c r="E59">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F59">
         <v>1967</v>
@@ -9281,7 +9281,7 @@
         <v>14</v>
       </c>
       <c r="E60">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F60">
         <v>1967</v>
@@ -9337,7 +9337,7 @@
         <v>14</v>
       </c>
       <c r="E61">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F61">
         <v>1967</v>
@@ -9393,7 +9393,7 @@
         <v>14</v>
       </c>
       <c r="E62">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F62">
         <v>1967</v>
@@ -9449,7 +9449,7 @@
         <v>14</v>
       </c>
       <c r="E63">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F63">
         <v>1967</v>
@@ -9505,7 +9505,7 @@
         <v>14</v>
       </c>
       <c r="E64">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F64">
         <v>1967</v>
@@ -9561,7 +9561,7 @@
         <v>14</v>
       </c>
       <c r="E65">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F65">
         <v>1967</v>
@@ -9617,7 +9617,7 @@
         <v>14</v>
       </c>
       <c r="E66">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F66">
         <v>1967</v>
@@ -9673,7 +9673,7 @@
         <v>14</v>
       </c>
       <c r="E67">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F67">
         <v>1967</v>
@@ -9729,7 +9729,7 @@
         <v>14</v>
       </c>
       <c r="E68">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F68">
         <v>1967</v>
@@ -9785,19 +9785,19 @@
         <v>14</v>
       </c>
       <c r="E69">
-        <v>0.24528</v>
+        <v>0.26405904000000002</v>
       </c>
       <c r="F69">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G69">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H69">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I69">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J69" t="s">
         <v>72</v>
@@ -9841,19 +9841,19 @@
         <v>14</v>
       </c>
       <c r="E70">
-        <v>0.24528</v>
+        <v>0.26405904000000002</v>
       </c>
       <c r="F70">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G70">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H70">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I70">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J70" t="s">
         <v>73</v>
@@ -9897,19 +9897,19 @@
         <v>14</v>
       </c>
       <c r="E71">
-        <v>0.24528</v>
+        <v>0.26405904000000002</v>
       </c>
       <c r="F71">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G71">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H71">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I71">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J71" t="s">
         <v>74</v>
@@ -9953,7 +9953,7 @@
         <v>14</v>
       </c>
       <c r="E72">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F72">
         <v>1967</v>
@@ -10009,7 +10009,7 @@
         <v>14</v>
       </c>
       <c r="E73">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F73">
         <v>1967</v>
@@ -10065,7 +10065,7 @@
         <v>14</v>
       </c>
       <c r="E74">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F74">
         <v>1967</v>
@@ -10121,7 +10121,7 @@
         <v>14</v>
       </c>
       <c r="E75">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F75">
         <v>1967</v>
@@ -10177,7 +10177,7 @@
         <v>14</v>
       </c>
       <c r="E76">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F76">
         <v>1967</v>
@@ -10233,7 +10233,7 @@
         <v>14</v>
       </c>
       <c r="E77">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F77">
         <v>1967</v>
@@ -10289,7 +10289,7 @@
         <v>14</v>
       </c>
       <c r="E78">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F78">
         <v>1967</v>
@@ -10345,7 +10345,7 @@
         <v>14</v>
       </c>
       <c r="E79">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F79">
         <v>1967</v>
@@ -10401,7 +10401,7 @@
         <v>14</v>
       </c>
       <c r="E80">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F80">
         <v>1967</v>
@@ -10457,7 +10457,7 @@
         <v>14</v>
       </c>
       <c r="E81">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F81">
         <v>1967</v>
@@ -10513,7 +10513,7 @@
         <v>14</v>
       </c>
       <c r="E82">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F82">
         <v>1967</v>
@@ -10569,7 +10569,7 @@
         <v>14</v>
       </c>
       <c r="E83">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F83">
         <v>1967</v>
@@ -10625,7 +10625,7 @@
         <v>14</v>
       </c>
       <c r="E84">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F84">
         <v>1967</v>
@@ -10681,7 +10681,7 @@
         <v>14</v>
       </c>
       <c r="E85">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F85">
         <v>1967</v>
@@ -10737,7 +10737,7 @@
         <v>14</v>
       </c>
       <c r="E86">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F86">
         <v>1967</v>
@@ -10793,7 +10793,7 @@
         <v>14</v>
       </c>
       <c r="E87">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F87">
         <v>1967</v>
@@ -10849,7 +10849,7 @@
         <v>14</v>
       </c>
       <c r="E88">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F88">
         <v>1967</v>
@@ -10905,7 +10905,7 @@
         <v>14</v>
       </c>
       <c r="E89">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F89">
         <v>1967</v>
@@ -10961,7 +10961,7 @@
         <v>14</v>
       </c>
       <c r="E90">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F90">
         <v>1967</v>
@@ -11017,7 +11017,7 @@
         <v>14</v>
       </c>
       <c r="E91">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F91">
         <v>1967</v>
@@ -11073,7 +11073,7 @@
         <v>14</v>
       </c>
       <c r="E92">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F92">
         <v>1967</v>
@@ -11129,7 +11129,7 @@
         <v>14</v>
       </c>
       <c r="E93">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F93">
         <v>1967</v>
@@ -11185,7 +11185,7 @@
         <v>14</v>
       </c>
       <c r="E94">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F94">
         <v>1967</v>
@@ -11241,7 +11241,7 @@
         <v>14</v>
       </c>
       <c r="E95">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F95">
         <v>1967</v>
@@ -11297,7 +11297,7 @@
         <v>14</v>
       </c>
       <c r="E96">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F96">
         <v>1967</v>
@@ -11353,19 +11353,19 @@
         <v>14</v>
       </c>
       <c r="E97">
-        <v>0.24528</v>
+        <v>0.26405904000000002</v>
       </c>
       <c r="F97">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G97">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H97">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I97">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J97" t="s">
         <v>100</v>
@@ -11409,19 +11409,19 @@
         <v>14</v>
       </c>
       <c r="E98">
-        <v>0.24528</v>
+        <v>0.26405904000000002</v>
       </c>
       <c r="F98">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G98">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H98">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I98">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J98" t="s">
         <v>101</v>
@@ -11465,19 +11465,19 @@
         <v>14</v>
       </c>
       <c r="E99">
-        <v>0.24528</v>
+        <v>0.26405904000000002</v>
       </c>
       <c r="F99">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G99">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H99">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I99">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J99" t="s">
         <v>102</v>
@@ -11521,7 +11521,7 @@
         <v>14</v>
       </c>
       <c r="E100">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F100">
         <v>1967</v>
@@ -11577,7 +11577,7 @@
         <v>14</v>
       </c>
       <c r="E101">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F101">
         <v>1967</v>
@@ -11633,19 +11633,19 @@
         <v>14</v>
       </c>
       <c r="E102">
-        <v>0.24528</v>
+        <v>0.26405904000000002</v>
       </c>
       <c r="F102">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G102">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H102">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I102">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J102" t="s">
         <v>105</v>
@@ -11689,19 +11689,19 @@
         <v>14</v>
       </c>
       <c r="E103">
-        <v>0.24528</v>
+        <v>0.26405904000000002</v>
       </c>
       <c r="F103">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G103">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H103">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I103">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J103" t="s">
         <v>106</v>
@@ -11745,7 +11745,7 @@
         <v>14</v>
       </c>
       <c r="E104">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F104">
         <v>1967</v>
@@ -11801,7 +11801,7 @@
         <v>14</v>
       </c>
       <c r="E105">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F105">
         <v>1967</v>
@@ -11857,7 +11857,7 @@
         <v>14</v>
       </c>
       <c r="E106">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F106">
         <v>1967</v>
@@ -11913,7 +11913,7 @@
         <v>14</v>
       </c>
       <c r="E107">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F107">
         <v>1967</v>
@@ -11969,7 +11969,7 @@
         <v>14</v>
       </c>
       <c r="E108">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F108">
         <v>1967</v>
@@ -12025,7 +12025,7 @@
         <v>14</v>
       </c>
       <c r="E109">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F109">
         <v>1967</v>
@@ -12081,7 +12081,7 @@
         <v>14</v>
       </c>
       <c r="E110">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F110">
         <v>1967</v>
@@ -12137,7 +12137,7 @@
         <v>14</v>
       </c>
       <c r="E111">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F111">
         <v>1967</v>
@@ -12193,7 +12193,7 @@
         <v>14</v>
       </c>
       <c r="E112">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F112">
         <v>1967</v>
@@ -12249,7 +12249,7 @@
         <v>14</v>
       </c>
       <c r="E113">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F113">
         <v>1967</v>
@@ -12305,7 +12305,7 @@
         <v>14</v>
       </c>
       <c r="E114">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F114">
         <v>1967</v>
@@ -12361,7 +12361,7 @@
         <v>14</v>
       </c>
       <c r="E115">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F115">
         <v>1967</v>
@@ -12417,7 +12417,7 @@
         <v>14</v>
       </c>
       <c r="E116">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F116">
         <v>1967</v>
@@ -12473,7 +12473,7 @@
         <v>14</v>
       </c>
       <c r="E117">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F117">
         <v>1967</v>
@@ -12529,7 +12529,7 @@
         <v>14</v>
       </c>
       <c r="E118">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F118">
         <v>1967</v>
@@ -12585,7 +12585,7 @@
         <v>14</v>
       </c>
       <c r="E119">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F119">
         <v>1967</v>
@@ -12641,19 +12641,19 @@
         <v>14</v>
       </c>
       <c r="E120">
-        <v>0.24528</v>
+        <v>0.26405904000000002</v>
       </c>
       <c r="F120">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G120">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H120">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I120">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J120" t="s">
         <v>123</v>
@@ -12697,19 +12697,19 @@
         <v>14</v>
       </c>
       <c r="E121">
-        <v>0.24528</v>
+        <v>0.26405904000000002</v>
       </c>
       <c r="F121">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G121">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H121">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I121">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J121" t="s">
         <v>124</v>
@@ -12753,7 +12753,7 @@
         <v>14</v>
       </c>
       <c r="E122">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F122">
         <v>1967</v>
@@ -12809,7 +12809,7 @@
         <v>14</v>
       </c>
       <c r="E123">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F123">
         <v>1967</v>
@@ -12865,7 +12865,7 @@
         <v>14</v>
       </c>
       <c r="E124">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F124">
         <v>1967</v>
@@ -12921,7 +12921,7 @@
         <v>14</v>
       </c>
       <c r="E125">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F125">
         <v>1967</v>
@@ -12977,7 +12977,7 @@
         <v>14</v>
       </c>
       <c r="E126">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F126">
         <v>1967</v>
@@ -13033,7 +13033,7 @@
         <v>14</v>
       </c>
       <c r="E127">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F127">
         <v>1967</v>
@@ -13089,7 +13089,7 @@
         <v>14</v>
       </c>
       <c r="E128">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F128">
         <v>1967</v>
@@ -13145,7 +13145,7 @@
         <v>14</v>
       </c>
       <c r="E129">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F129">
         <v>1967</v>
@@ -13201,7 +13201,7 @@
         <v>14</v>
       </c>
       <c r="E130">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F130">
         <v>1967</v>
@@ -13257,7 +13257,7 @@
         <v>14</v>
       </c>
       <c r="E131">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F131">
         <v>1967</v>
@@ -13313,7 +13313,7 @@
         <v>14</v>
       </c>
       <c r="E132">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F132">
         <v>1967</v>
@@ -13369,7 +13369,7 @@
         <v>14</v>
       </c>
       <c r="E133">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F133">
         <v>1967</v>
@@ -13425,19 +13425,19 @@
         <v>14</v>
       </c>
       <c r="E134">
-        <v>0.24528</v>
+        <v>0.26405904000000002</v>
       </c>
       <c r="F134">
-        <v>2200</v>
+        <v>1967</v>
       </c>
       <c r="G134">
-        <v>27.7</v>
+        <v>25.2</v>
       </c>
       <c r="H134">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="I134">
-        <v>0.74765000000000004</v>
+        <v>0.76759999999999995</v>
       </c>
       <c r="J134" t="s">
         <v>137</v>
@@ -13481,7 +13481,7 @@
         <v>14</v>
       </c>
       <c r="E135">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F135">
         <v>1967</v>
@@ -13537,7 +13537,7 @@
         <v>14</v>
       </c>
       <c r="E136">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F136">
         <v>1967</v>
@@ -13593,7 +13593,7 @@
         <v>14</v>
       </c>
       <c r="E137">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F137">
         <v>1967</v>
@@ -13649,7 +13649,7 @@
         <v>14</v>
       </c>
       <c r="E138">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F138">
         <v>1967</v>
@@ -13705,7 +13705,7 @@
         <v>14</v>
       </c>
       <c r="E139">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F139">
         <v>1967</v>
@@ -13761,7 +13761,7 @@
         <v>14</v>
       </c>
       <c r="E140">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F140">
         <v>1967</v>
@@ -13817,7 +13817,7 @@
         <v>14</v>
       </c>
       <c r="E141">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F141">
         <v>1967</v>
@@ -13873,7 +13873,7 @@
         <v>14</v>
       </c>
       <c r="E142">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F142">
         <v>1967</v>
@@ -13929,7 +13929,7 @@
         <v>14</v>
       </c>
       <c r="E143">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F143">
         <v>1967</v>
@@ -13985,7 +13985,7 @@
         <v>14</v>
       </c>
       <c r="E144">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F144">
         <v>1967</v>
@@ -14041,7 +14041,7 @@
         <v>14</v>
       </c>
       <c r="E145">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F145">
         <v>1967</v>
@@ -14097,7 +14097,7 @@
         <v>14</v>
       </c>
       <c r="E146">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F146">
         <v>1967</v>
@@ -14153,7 +14153,7 @@
         <v>14</v>
       </c>
       <c r="E147">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F147">
         <v>1967</v>
@@ -14209,7 +14209,7 @@
         <v>14</v>
       </c>
       <c r="E148">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F148">
         <v>1967</v>
@@ -14265,7 +14265,7 @@
         <v>14</v>
       </c>
       <c r="E149">
-        <v>0.26369279999999995</v>
+        <v>0.27160358399999995</v>
       </c>
       <c r="F149">
         <v>1967</v>
@@ -14321,7 +14321,7 @@
         <v>14</v>
       </c>
       <c r="E150">
-        <v>9.9225600000000025E-2</v>
+        <v>0.10220236800000004</v>
       </c>
       <c r="F150">
         <v>3583</v>
@@ -14377,7 +14377,7 @@
         <v>14</v>
       </c>
       <c r="E151">
-        <v>9.9225600000000025E-2</v>
+        <v>0.10220236800000004</v>
       </c>
       <c r="F151">
         <v>3583</v>
@@ -14433,7 +14433,7 @@
         <v>14</v>
       </c>
       <c r="E152">
-        <v>9.9225600000000025E-2</v>
+        <v>0.10220236800000004</v>
       </c>
       <c r="F152">
         <v>3583</v>
@@ -14489,7 +14489,7 @@
         <v>14</v>
       </c>
       <c r="E153">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F153">
         <v>3583</v>
@@ -14545,7 +14545,7 @@
         <v>14</v>
       </c>
       <c r="E154">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F154">
         <v>3583</v>
@@ -14601,7 +14601,7 @@
         <v>14</v>
       </c>
       <c r="E155">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F155">
         <v>3583</v>
@@ -14657,7 +14657,7 @@
         <v>14</v>
       </c>
       <c r="E156">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F156">
         <v>3583</v>
@@ -14713,7 +14713,7 @@
         <v>14</v>
       </c>
       <c r="E157">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F157">
         <v>3583</v>
@@ -14769,7 +14769,7 @@
         <v>14</v>
       </c>
       <c r="E158">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F158">
         <v>3583</v>
@@ -14825,7 +14825,7 @@
         <v>14</v>
       </c>
       <c r="E159">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F159">
         <v>3583</v>
@@ -14881,7 +14881,7 @@
         <v>14</v>
       </c>
       <c r="E160">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F160">
         <v>3583</v>
@@ -14937,7 +14937,7 @@
         <v>14</v>
       </c>
       <c r="E161">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F161">
         <v>3583</v>
@@ -14993,7 +14993,7 @@
         <v>14</v>
       </c>
       <c r="E162">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F162">
         <v>3583</v>
@@ -15049,7 +15049,7 @@
         <v>14</v>
       </c>
       <c r="E163">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F163">
         <v>3583</v>
@@ -15105,7 +15105,7 @@
         <v>14</v>
       </c>
       <c r="E164">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F164">
         <v>3583</v>
@@ -15161,7 +15161,7 @@
         <v>14</v>
       </c>
       <c r="E165">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F165">
         <v>3583</v>
@@ -15217,7 +15217,7 @@
         <v>14</v>
       </c>
       <c r="E166">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F166">
         <v>3583</v>
@@ -15273,7 +15273,7 @@
         <v>14</v>
       </c>
       <c r="E167">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F167">
         <v>3583</v>
@@ -15329,7 +15329,7 @@
         <v>14</v>
       </c>
       <c r="E168">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F168">
         <v>3583</v>
@@ -15385,7 +15385,7 @@
         <v>14</v>
       </c>
       <c r="E169">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F169">
         <v>3583</v>
@@ -15441,7 +15441,7 @@
         <v>14</v>
       </c>
       <c r="E170">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F170">
         <v>3583</v>
@@ -15497,7 +15497,7 @@
         <v>14</v>
       </c>
       <c r="E171">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F171">
         <v>3583</v>
@@ -15553,7 +15553,7 @@
         <v>14</v>
       </c>
       <c r="E172">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F172">
         <v>3583</v>
@@ -15609,7 +15609,7 @@
         <v>14</v>
       </c>
       <c r="E173">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F173">
         <v>3583</v>
@@ -15665,7 +15665,7 @@
         <v>14</v>
       </c>
       <c r="E174">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F174">
         <v>3583</v>
@@ -15721,7 +15721,7 @@
         <v>14</v>
       </c>
       <c r="E175">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F175">
         <v>3583</v>
@@ -15777,7 +15777,7 @@
         <v>14</v>
       </c>
       <c r="E176">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F176">
         <v>3583</v>
@@ -15833,7 +15833,7 @@
         <v>14</v>
       </c>
       <c r="E177">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F177">
         <v>3583</v>
@@ -15889,7 +15889,7 @@
         <v>14</v>
       </c>
       <c r="E178">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F178">
         <v>3583</v>
@@ -15945,7 +15945,7 @@
         <v>14</v>
       </c>
       <c r="E179">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F179">
         <v>3583</v>
@@ -16001,7 +16001,7 @@
         <v>14</v>
       </c>
       <c r="E180">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F180">
         <v>3583</v>
@@ -16057,7 +16057,7 @@
         <v>14</v>
       </c>
       <c r="E181">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F181">
         <v>3583</v>
@@ -16113,7 +16113,7 @@
         <v>14</v>
       </c>
       <c r="E182">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F182">
         <v>3583</v>
@@ -16169,7 +16169,7 @@
         <v>14</v>
       </c>
       <c r="E183">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F183">
         <v>3583</v>
@@ -16225,7 +16225,7 @@
         <v>14</v>
       </c>
       <c r="E184">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F184">
         <v>3583</v>
@@ -16281,7 +16281,7 @@
         <v>14</v>
       </c>
       <c r="E185">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F185">
         <v>3583</v>
@@ -16337,7 +16337,7 @@
         <v>14</v>
       </c>
       <c r="E186">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F186">
         <v>3583</v>
@@ -16393,7 +16393,7 @@
         <v>14</v>
       </c>
       <c r="E187">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F187">
         <v>3583</v>
@@ -16449,7 +16449,7 @@
         <v>14</v>
       </c>
       <c r="E188">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F188">
         <v>3583</v>
@@ -16505,7 +16505,7 @@
         <v>14</v>
       </c>
       <c r="E189">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F189">
         <v>3583</v>
@@ -16561,7 +16561,7 @@
         <v>14</v>
       </c>
       <c r="E190">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F190">
         <v>3583</v>
@@ -16617,7 +16617,7 @@
         <v>14</v>
       </c>
       <c r="E191">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F191">
         <v>3583</v>
@@ -16673,7 +16673,7 @@
         <v>14</v>
       </c>
       <c r="E192">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F192">
         <v>3583</v>
@@ -16729,7 +16729,7 @@
         <v>14</v>
       </c>
       <c r="E193">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F193">
         <v>3583</v>
@@ -16785,7 +16785,7 @@
         <v>14</v>
       </c>
       <c r="E194">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F194">
         <v>3583</v>
@@ -16841,7 +16841,7 @@
         <v>14</v>
       </c>
       <c r="E195">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F195">
         <v>3583</v>
@@ -16897,7 +16897,7 @@
         <v>14</v>
       </c>
       <c r="E196">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F196">
         <v>3583</v>
@@ -16953,7 +16953,7 @@
         <v>14</v>
       </c>
       <c r="E197">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F197">
         <v>3583</v>
@@ -17009,7 +17009,7 @@
         <v>14</v>
       </c>
       <c r="E198">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F198">
         <v>3583</v>
@@ -17065,7 +17065,7 @@
         <v>14</v>
       </c>
       <c r="E199">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F199">
         <v>3583</v>
@@ -17121,7 +17121,7 @@
         <v>14</v>
       </c>
       <c r="E200">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F200">
         <v>3583</v>
@@ -17177,7 +17177,7 @@
         <v>14</v>
       </c>
       <c r="E201">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F201">
         <v>3583</v>
@@ -17233,7 +17233,7 @@
         <v>14</v>
       </c>
       <c r="E202">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F202">
         <v>3583</v>
@@ -17289,7 +17289,7 @@
         <v>14</v>
       </c>
       <c r="E203">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F203">
         <v>3583</v>
@@ -17345,7 +17345,7 @@
         <v>14</v>
       </c>
       <c r="E204">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F204">
         <v>3583</v>
@@ -17401,7 +17401,7 @@
         <v>14</v>
       </c>
       <c r="E205">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F205">
         <v>3583</v>
@@ -17457,7 +17457,7 @@
         <v>14</v>
       </c>
       <c r="E206">
-        <v>0.1050624</v>
+        <v>0.108214272</v>
       </c>
       <c r="F206">
         <v>3583</v>
@@ -17513,7 +17513,7 @@
         <v>14</v>
       </c>
       <c r="E207">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F207">
         <v>1967</v>
@@ -17569,7 +17569,7 @@
         <v>14</v>
       </c>
       <c r="E208">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F208">
         <v>1967</v>
@@ -17625,7 +17625,7 @@
         <v>14</v>
       </c>
       <c r="E209">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F209">
         <v>1967</v>
@@ -17681,7 +17681,7 @@
         <v>14</v>
       </c>
       <c r="E210">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F210">
         <v>1967</v>
@@ -17737,7 +17737,7 @@
         <v>14</v>
       </c>
       <c r="E211">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F211">
         <v>1967</v>
@@ -17793,7 +17793,7 @@
         <v>14</v>
       </c>
       <c r="E212">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F212">
         <v>1967</v>
@@ -17849,7 +17849,7 @@
         <v>14</v>
       </c>
       <c r="E213">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F213">
         <v>1967</v>
@@ -17905,7 +17905,7 @@
         <v>14</v>
       </c>
       <c r="E214">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F214">
         <v>1967</v>
@@ -17961,7 +17961,7 @@
         <v>14</v>
       </c>
       <c r="E215">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F215">
         <v>1967</v>
@@ -18017,7 +18017,7 @@
         <v>14</v>
       </c>
       <c r="E216">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F216">
         <v>1967</v>
@@ -18073,7 +18073,7 @@
         <v>14</v>
       </c>
       <c r="E217">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F217">
         <v>1967</v>
@@ -18129,7 +18129,7 @@
         <v>14</v>
       </c>
       <c r="E218">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F218">
         <v>1967</v>
@@ -18185,7 +18185,7 @@
         <v>14</v>
       </c>
       <c r="E219">
-        <v>0.336648</v>
+        <v>0.34674743999999996</v>
       </c>
       <c r="F219">
         <v>1726</v>
@@ -18241,7 +18241,7 @@
         <v>14</v>
       </c>
       <c r="E220">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F220">
         <v>1967</v>
@@ -18297,7 +18297,7 @@
         <v>14</v>
       </c>
       <c r="E221">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F221">
         <v>1967</v>
@@ -18353,7 +18353,7 @@
         <v>14</v>
       </c>
       <c r="E222">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F222">
         <v>1967</v>
@@ -18409,7 +18409,7 @@
         <v>14</v>
       </c>
       <c r="E223">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F223">
         <v>1967</v>
@@ -18465,7 +18465,7 @@
         <v>14</v>
       </c>
       <c r="E224">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F224">
         <v>1967</v>
@@ -18521,7 +18521,7 @@
         <v>14</v>
       </c>
       <c r="E225">
-        <v>0.30397919999999995</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F225">
         <v>1967</v>
@@ -18577,7 +18577,7 @@
         <v>14</v>
       </c>
       <c r="E226">
-        <v>0.30397919999999995</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F226">
         <v>1967</v>
@@ -18633,7 +18633,7 @@
         <v>14</v>
       </c>
       <c r="E227">
-        <v>0.336648</v>
+        <v>0.34674743999999996</v>
       </c>
       <c r="F227">
         <v>1726</v>
@@ -18689,7 +18689,7 @@
         <v>14</v>
       </c>
       <c r="E228">
-        <v>0.34476000000000001</v>
+        <v>0.3551028</v>
       </c>
       <c r="F228">
         <v>1726</v>
@@ -18745,7 +18745,7 @@
         <v>14</v>
       </c>
       <c r="E229">
-        <v>0.34476000000000001</v>
+        <v>0.3551028</v>
       </c>
       <c r="F229">
         <v>1726</v>
@@ -18801,7 +18801,7 @@
         <v>14</v>
       </c>
       <c r="E230">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F230">
         <v>1967</v>
@@ -18857,7 +18857,7 @@
         <v>14</v>
       </c>
       <c r="E231">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F231">
         <v>1967</v>
@@ -18913,7 +18913,7 @@
         <v>14</v>
       </c>
       <c r="E232">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F232">
         <v>1967</v>
@@ -18969,7 +18969,7 @@
         <v>14</v>
       </c>
       <c r="E233">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F233">
         <v>1967</v>
@@ -19025,7 +19025,7 @@
         <v>14</v>
       </c>
       <c r="E234">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F234">
         <v>1967</v>
@@ -19081,7 +19081,7 @@
         <v>14</v>
       </c>
       <c r="E235">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F235">
         <v>1967</v>
@@ -19137,7 +19137,7 @@
         <v>14</v>
       </c>
       <c r="E236">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F236">
         <v>1967</v>
@@ -19193,7 +19193,7 @@
         <v>14</v>
       </c>
       <c r="E237">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F237">
         <v>1967</v>
@@ -19249,7 +19249,7 @@
         <v>14</v>
       </c>
       <c r="E238">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F238">
         <v>1967</v>
@@ -19305,7 +19305,7 @@
         <v>14</v>
       </c>
       <c r="E239">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F239">
         <v>1967</v>
@@ -19361,7 +19361,7 @@
         <v>14</v>
       </c>
       <c r="E240">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F240">
         <v>1967</v>
@@ -19417,7 +19417,7 @@
         <v>14</v>
       </c>
       <c r="E241">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F241">
         <v>1967</v>
@@ -19473,7 +19473,7 @@
         <v>14</v>
       </c>
       <c r="E242">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F242">
         <v>1967</v>
@@ -19529,7 +19529,7 @@
         <v>14</v>
       </c>
       <c r="E243">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F243">
         <v>1967</v>
@@ -19585,7 +19585,7 @@
         <v>14</v>
       </c>
       <c r="E244">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F244">
         <v>1967</v>
@@ -19641,7 +19641,7 @@
         <v>14</v>
       </c>
       <c r="E245">
-        <v>0.30397919999999995</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F245">
         <v>1967</v>
@@ -19697,7 +19697,7 @@
         <v>14</v>
       </c>
       <c r="E246">
-        <v>0.30397919999999995</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F246">
         <v>1967</v>
@@ -19753,7 +19753,7 @@
         <v>14</v>
       </c>
       <c r="E247">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F247">
         <v>1967</v>
@@ -19809,7 +19809,7 @@
         <v>14</v>
       </c>
       <c r="E248">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F248">
         <v>1967</v>
@@ -19865,7 +19865,7 @@
         <v>14</v>
       </c>
       <c r="E249">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F249">
         <v>1967</v>
@@ -19921,7 +19921,7 @@
         <v>14</v>
       </c>
       <c r="E250">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F250">
         <v>1967</v>
@@ -19977,7 +19977,7 @@
         <v>14</v>
       </c>
       <c r="E251">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F251">
         <v>1967</v>
@@ -20033,7 +20033,7 @@
         <v>14</v>
       </c>
       <c r="E252">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F252">
         <v>1967</v>
@@ -20089,7 +20089,7 @@
         <v>14</v>
       </c>
       <c r="E253">
-        <v>0.30397919999999995</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F253">
         <v>1967</v>
@@ -20145,7 +20145,7 @@
         <v>14</v>
       </c>
       <c r="E254">
-        <v>0.336648</v>
+        <v>0.34674743999999996</v>
       </c>
       <c r="F254">
         <v>1726</v>
@@ -20201,7 +20201,7 @@
         <v>14</v>
       </c>
       <c r="E255">
-        <v>0.30397919999999995</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F255">
         <v>1967</v>
@@ -20257,7 +20257,7 @@
         <v>14</v>
       </c>
       <c r="E256">
-        <v>0.30397919999999995</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F256">
         <v>1967</v>
@@ -20313,7 +20313,7 @@
         <v>14</v>
       </c>
       <c r="E257">
-        <v>0.30397919999999995</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F257">
         <v>1967</v>
@@ -20369,7 +20369,7 @@
         <v>14</v>
       </c>
       <c r="E258">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F258">
         <v>1967</v>
@@ -20425,7 +20425,7 @@
         <v>14</v>
       </c>
       <c r="E259">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F259">
         <v>1967</v>
@@ -20481,7 +20481,7 @@
         <v>14</v>
       </c>
       <c r="E260">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F260">
         <v>1967</v>
@@ -20537,7 +20537,7 @@
         <v>14</v>
       </c>
       <c r="E261">
-        <v>0.336648</v>
+        <v>0.34674743999999996</v>
       </c>
       <c r="F261">
         <v>1726</v>
@@ -20593,7 +20593,7 @@
         <v>14</v>
       </c>
       <c r="E262">
-        <v>0.336648</v>
+        <v>0.34674743999999996</v>
       </c>
       <c r="F262">
         <v>1726</v>
@@ -20649,7 +20649,7 @@
         <v>14</v>
       </c>
       <c r="E263">
-        <v>0.336648</v>
+        <v>0.34674743999999996</v>
       </c>
       <c r="F263">
         <v>1726</v>
@@ -20705,7 +20705,7 @@
         <v>14</v>
       </c>
       <c r="E264">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F264">
         <v>1967</v>
@@ -20761,7 +20761,7 @@
         <v>14</v>
       </c>
       <c r="E265">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F265">
         <v>1967</v>
@@ -20817,7 +20817,7 @@
         <v>14</v>
       </c>
       <c r="E266">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F266">
         <v>1967</v>
@@ -20873,7 +20873,7 @@
         <v>14</v>
       </c>
       <c r="E267">
-        <v>0.336648</v>
+        <v>0.34674743999999996</v>
       </c>
       <c r="F267">
         <v>1726</v>
@@ -20929,7 +20929,7 @@
         <v>14</v>
       </c>
       <c r="E268">
-        <v>0.336648</v>
+        <v>0.34674743999999996</v>
       </c>
       <c r="F268">
         <v>1726</v>
@@ -20985,7 +20985,7 @@
         <v>14</v>
       </c>
       <c r="E269">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F269">
         <v>1967</v>
@@ -21041,7 +21041,7 @@
         <v>14</v>
       </c>
       <c r="E270">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F270">
         <v>1967</v>
@@ -21097,7 +21097,7 @@
         <v>14</v>
       </c>
       <c r="E271">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F271">
         <v>1967</v>
@@ -21153,7 +21153,7 @@
         <v>14</v>
       </c>
       <c r="E272">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F272">
         <v>1967</v>
@@ -21209,7 +21209,7 @@
         <v>14</v>
       </c>
       <c r="E273">
-        <v>0.30397919999999995</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F273">
         <v>1967</v>
@@ -21265,7 +21265,7 @@
         <v>14</v>
       </c>
       <c r="E274">
-        <v>0.28932959999999996</v>
+        <v>0.29800948799999993</v>
       </c>
       <c r="F274">
         <v>1967</v>
@@ -21321,7 +21321,7 @@
         <v>14</v>
       </c>
       <c r="E275">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F275">
         <v>1967</v>
@@ -21377,7 +21377,7 @@
         <v>14</v>
       </c>
       <c r="E276">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F276">
         <v>1967</v>
@@ -21433,7 +21433,7 @@
         <v>14</v>
       </c>
       <c r="E277">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F277">
         <v>1967</v>
@@ -21489,7 +21489,7 @@
         <v>14</v>
       </c>
       <c r="E278">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F278">
         <v>1967</v>
@@ -21545,7 +21545,7 @@
         <v>14</v>
       </c>
       <c r="E279">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F279">
         <v>1967</v>
@@ -21601,7 +21601,7 @@
         <v>14</v>
       </c>
       <c r="E280">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F280">
         <v>1967</v>
@@ -21657,7 +21657,7 @@
         <v>14</v>
       </c>
       <c r="E281">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F281">
         <v>1967</v>
@@ -21713,7 +21713,7 @@
         <v>14</v>
       </c>
       <c r="E282">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F282">
         <v>1967</v>
@@ -21769,7 +21769,7 @@
         <v>14</v>
       </c>
       <c r="E283">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F283">
         <v>1967</v>
@@ -21825,7 +21825,7 @@
         <v>14</v>
       </c>
       <c r="E284">
-        <v>0.34476000000000001</v>
+        <v>0.3551028</v>
       </c>
       <c r="F284">
         <v>1726</v>
@@ -21881,7 +21881,7 @@
         <v>14</v>
       </c>
       <c r="E285">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F285">
         <v>1967</v>
@@ -21937,7 +21937,7 @@
         <v>14</v>
       </c>
       <c r="E286">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F286">
         <v>1967</v>
@@ -21993,7 +21993,7 @@
         <v>14</v>
       </c>
       <c r="E287">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F287">
         <v>1967</v>
@@ -22049,7 +22049,7 @@
         <v>14</v>
       </c>
       <c r="E288">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F288">
         <v>1967</v>
@@ -22105,7 +22105,7 @@
         <v>14</v>
       </c>
       <c r="E289">
-        <v>0.34476000000000001</v>
+        <v>0.3551028</v>
       </c>
       <c r="F289">
         <v>1726</v>
@@ -22161,7 +22161,7 @@
         <v>14</v>
       </c>
       <c r="E290">
-        <v>0.34476000000000001</v>
+        <v>0.3551028</v>
       </c>
       <c r="F290">
         <v>1726</v>
@@ -22217,7 +22217,7 @@
         <v>14</v>
       </c>
       <c r="E291">
-        <v>0.34476000000000001</v>
+        <v>0.3551028</v>
       </c>
       <c r="F291">
         <v>1726</v>
@@ -22273,7 +22273,7 @@
         <v>14</v>
       </c>
       <c r="E292">
-        <v>0.30397919999999995</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F292">
         <v>1967</v>
@@ -22329,7 +22329,7 @@
         <v>14</v>
       </c>
       <c r="E293">
-        <v>0.30397919999999995</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F293">
         <v>1967</v>
@@ -22385,7 +22385,7 @@
         <v>14</v>
       </c>
       <c r="E294">
-        <v>0.30397919999999995</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F294">
         <v>1967</v>
@@ -22441,7 +22441,7 @@
         <v>14</v>
       </c>
       <c r="E295">
-        <v>0.30397919999999995</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F295">
         <v>1967</v>
@@ -22497,7 +22497,7 @@
         <v>14</v>
       </c>
       <c r="E296">
-        <v>0.336648</v>
+        <v>0.34674743999999996</v>
       </c>
       <c r="F296">
         <v>1726</v>
@@ -22553,7 +22553,7 @@
         <v>14</v>
       </c>
       <c r="E297">
-        <v>0.336648</v>
+        <v>0.34674743999999996</v>
       </c>
       <c r="F297">
         <v>1726</v>
@@ -22609,7 +22609,7 @@
         <v>14</v>
       </c>
       <c r="E298">
-        <v>0.34476000000000001</v>
+        <v>0.3551028</v>
       </c>
       <c r="F298">
         <v>1726</v>
@@ -22665,7 +22665,7 @@
         <v>14</v>
       </c>
       <c r="E299">
-        <v>0.34476000000000001</v>
+        <v>0.3551028</v>
       </c>
       <c r="F299">
         <v>1726</v>
@@ -22721,7 +22721,7 @@
         <v>14</v>
       </c>
       <c r="E300">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F300">
         <v>1967</v>
@@ -22777,7 +22777,7 @@
         <v>14</v>
       </c>
       <c r="E301">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F301">
         <v>1967</v>
@@ -22833,7 +22833,7 @@
         <v>14</v>
       </c>
       <c r="E302">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F302">
         <v>1967</v>
@@ -22889,7 +22889,7 @@
         <v>14</v>
       </c>
       <c r="E303">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F303">
         <v>1967</v>
@@ -22945,7 +22945,7 @@
         <v>14</v>
       </c>
       <c r="E304">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F304">
         <v>1967</v>
@@ -23001,7 +23001,7 @@
         <v>14</v>
       </c>
       <c r="E305">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F305">
         <v>1967</v>
@@ -23057,7 +23057,7 @@
         <v>14</v>
       </c>
       <c r="E306">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F306">
         <v>1967</v>
@@ -23113,7 +23113,7 @@
         <v>14</v>
       </c>
       <c r="E307">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F307">
         <v>1967</v>
@@ -23169,7 +23169,7 @@
         <v>14</v>
       </c>
       <c r="E308">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F308">
         <v>1967</v>
@@ -23225,7 +23225,7 @@
         <v>14</v>
       </c>
       <c r="E309">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F309">
         <v>1967</v>
@@ -23281,7 +23281,7 @@
         <v>14</v>
       </c>
       <c r="E310">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F310">
         <v>1967</v>
@@ -23337,7 +23337,7 @@
         <v>14</v>
       </c>
       <c r="E311">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F311">
         <v>1967</v>
@@ -23393,7 +23393,7 @@
         <v>14</v>
       </c>
       <c r="E312">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F312">
         <v>1967</v>
@@ -23449,7 +23449,7 @@
         <v>14</v>
       </c>
       <c r="E313">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F313">
         <v>1967</v>
@@ -23505,7 +23505,7 @@
         <v>14</v>
       </c>
       <c r="E314">
-        <v>0.336648</v>
+        <v>0.34674743999999996</v>
       </c>
       <c r="F314">
         <v>1726</v>
@@ -23561,7 +23561,7 @@
         <v>14</v>
       </c>
       <c r="E315">
-        <v>0.336648</v>
+        <v>0.34674743999999996</v>
       </c>
       <c r="F315">
         <v>1726</v>
@@ -23617,7 +23617,7 @@
         <v>14</v>
       </c>
       <c r="E316">
-        <v>0.34476000000000001</v>
+        <v>0.3551028</v>
       </c>
       <c r="F316">
         <v>1726</v>
@@ -23673,7 +23673,7 @@
         <v>14</v>
       </c>
       <c r="E317">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F317">
         <v>1967</v>
@@ -23729,7 +23729,7 @@
         <v>14</v>
       </c>
       <c r="E318">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F318">
         <v>1967</v>
@@ -23785,7 +23785,7 @@
         <v>14</v>
       </c>
       <c r="E319">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F319">
         <v>1967</v>
@@ -23841,7 +23841,7 @@
         <v>14</v>
       </c>
       <c r="E320">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F320">
         <v>1967</v>
@@ -23876,7 +23876,7 @@
         <v>14</v>
       </c>
       <c r="E321">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F321">
         <v>1967</v>
@@ -23911,7 +23911,7 @@
         <v>14</v>
       </c>
       <c r="E322">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F322">
         <v>1967</v>
@@ -23946,7 +23946,7 @@
         <v>14</v>
       </c>
       <c r="E323">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F323">
         <v>1967</v>
@@ -23981,7 +23981,7 @@
         <v>14</v>
       </c>
       <c r="E324">
-        <v>0.336648</v>
+        <v>0.34674743999999996</v>
       </c>
       <c r="F324">
         <v>1726</v>
@@ -24016,7 +24016,7 @@
         <v>14</v>
       </c>
       <c r="E325">
-        <v>0.336648</v>
+        <v>0.34674743999999996</v>
       </c>
       <c r="F325">
         <v>1726</v>
@@ -24051,7 +24051,7 @@
         <v>14</v>
       </c>
       <c r="E326">
-        <v>0.336648</v>
+        <v>0.34674743999999996</v>
       </c>
       <c r="F326">
         <v>1726</v>
@@ -24086,7 +24086,7 @@
         <v>14</v>
       </c>
       <c r="E327">
-        <v>0.336648</v>
+        <v>0.34674743999999996</v>
       </c>
       <c r="F327">
         <v>1726</v>
@@ -24121,7 +24121,7 @@
         <v>14</v>
       </c>
       <c r="E328">
-        <v>0.336648</v>
+        <v>0.34674743999999996</v>
       </c>
       <c r="F328">
         <v>1726</v>
@@ -24156,7 +24156,7 @@
         <v>14</v>
       </c>
       <c r="E329">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F329">
         <v>1967</v>
@@ -24191,7 +24191,7 @@
         <v>14</v>
       </c>
       <c r="E330">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F330">
         <v>1967</v>
@@ -24226,7 +24226,7 @@
         <v>14</v>
       </c>
       <c r="E331">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F331">
         <v>1967</v>
@@ -24261,7 +24261,7 @@
         <v>14</v>
       </c>
       <c r="E332">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F332">
         <v>1967</v>
@@ -24296,7 +24296,7 @@
         <v>14</v>
       </c>
       <c r="E333">
-        <v>0.30397919999999989</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F333">
         <v>1967</v>
@@ -24331,7 +24331,7 @@
         <v>14</v>
       </c>
       <c r="E334">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F334">
         <v>1967</v>
@@ -24366,7 +24366,7 @@
         <v>14</v>
       </c>
       <c r="E335">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F335">
         <v>1967</v>
@@ -24401,7 +24401,7 @@
         <v>14</v>
       </c>
       <c r="E336">
-        <v>0.28932959999999996</v>
+        <v>0.29800948799999999</v>
       </c>
       <c r="F336">
         <v>1967</v>
@@ -24436,7 +24436,7 @@
         <v>14</v>
       </c>
       <c r="E337">
-        <v>0.30397919999999995</v>
+        <v>0.31309857599999996</v>
       </c>
       <c r="F337">
         <v>1967</v>
@@ -24471,7 +24471,7 @@
         <v>14</v>
       </c>
       <c r="E338">
-        <v>0.34476000000000001</v>
+        <v>0.3551028</v>
       </c>
       <c r="F338">
         <v>1726</v>
@@ -24506,7 +24506,7 @@
         <v>14</v>
       </c>
       <c r="E339">
-        <v>0.34476000000000001</v>
+        <v>0.3551028</v>
       </c>
       <c r="F339">
         <v>1726</v>
@@ -24541,7 +24541,7 @@
         <v>14</v>
       </c>
       <c r="E340">
-        <v>0.336648</v>
+        <v>0.34674743999999996</v>
       </c>
       <c r="F340">
         <v>1726</v>
@@ -24576,7 +24576,7 @@
         <v>14</v>
       </c>
       <c r="E341">
-        <v>0.34476000000000001</v>
+        <v>0.3551028</v>
       </c>
       <c r="F341">
         <v>1726</v>
@@ -24611,7 +24611,7 @@
         <v>14</v>
       </c>
       <c r="E342">
-        <v>0.34476000000000001</v>
+        <v>0.3551028</v>
       </c>
       <c r="F342">
         <v>1726</v>
@@ -24646,7 +24646,7 @@
         <v>14</v>
       </c>
       <c r="E343">
-        <v>0.34476000000000001</v>
+        <v>0.3551028</v>
       </c>
       <c r="F343">
         <v>1726</v>
@@ -24681,7 +24681,7 @@
         <v>14</v>
       </c>
       <c r="E344">
-        <v>0.34476000000000001</v>
+        <v>0.3551028</v>
       </c>
       <c r="F344">
         <v>1726</v>
@@ -24716,7 +24716,7 @@
         <v>14</v>
       </c>
       <c r="E345">
-        <v>0.34476000000000001</v>
+        <v>0.3551028</v>
       </c>
       <c r="F345">
         <v>1726</v>
@@ -24751,7 +24751,7 @@
         <v>14</v>
       </c>
       <c r="E346">
-        <v>0.336648</v>
+        <v>0.34674743999999996</v>
       </c>
       <c r="F346">
         <v>1726</v>
@@ -24786,7 +24786,7 @@
         <v>14</v>
       </c>
       <c r="E347">
-        <v>0.336648</v>
+        <v>0.34674743999999996</v>
       </c>
       <c r="F347">
         <v>1726</v>
@@ -24821,7 +24821,7 @@
         <v>14</v>
       </c>
       <c r="E348">
-        <v>0.31130399999999997</v>
+        <v>0.32064312</v>
       </c>
       <c r="F348">
         <v>1967</v>
@@ -24856,7 +24856,7 @@
         <v>14</v>
       </c>
       <c r="E349">
-        <v>0.31862879999999999</v>
+        <v>0.32818766399999999</v>
       </c>
       <c r="F349">
         <v>1967</v>
@@ -24891,7 +24891,7 @@
         <v>14</v>
       </c>
       <c r="E350">
-        <v>0.31862879999999999</v>
+        <v>0.32818766399999999</v>
       </c>
       <c r="F350">
         <v>1967</v>
@@ -24926,7 +24926,7 @@
         <v>14</v>
       </c>
       <c r="E351">
-        <v>0.36098399999999997</v>
+        <v>0.37181351999999995</v>
       </c>
       <c r="F351">
         <v>1726</v>
@@ -24961,7 +24961,7 @@
         <v>14</v>
       </c>
       <c r="E352">
-        <v>0.36098399999999997</v>
+        <v>0.37181351999999995</v>
       </c>
       <c r="F352">
         <v>1726</v>
@@ -24996,7 +24996,7 @@
         <v>14</v>
       </c>
       <c r="E353">
-        <v>0.32595360000000001</v>
+        <v>0.33573220799999992</v>
       </c>
       <c r="F353">
         <v>1967</v>
@@ -25031,7 +25031,7 @@
         <v>14</v>
       </c>
       <c r="E354">
-        <v>0.32595360000000001</v>
+        <v>0.33573220799999992</v>
       </c>
       <c r="F354">
         <v>1967</v>
@@ -25066,7 +25066,7 @@
         <v>14</v>
       </c>
       <c r="E355">
-        <v>0.36098399999999997</v>
+        <v>0.37181351999999995</v>
       </c>
       <c r="F355">
         <v>1726</v>
@@ -25101,7 +25101,7 @@
         <v>14</v>
       </c>
       <c r="E356">
-        <v>0.36098399999999997</v>
+        <v>0.37181351999999995</v>
       </c>
       <c r="F356">
         <v>1726</v>
@@ -25136,7 +25136,7 @@
         <v>14</v>
       </c>
       <c r="E357">
-        <v>0.32595360000000001</v>
+        <v>0.33573220799999992</v>
       </c>
       <c r="F357">
         <v>1967</v>
@@ -25171,7 +25171,7 @@
         <v>14</v>
       </c>
       <c r="E358">
-        <v>0.32595360000000001</v>
+        <v>0.33573220799999992</v>
       </c>
       <c r="F358">
         <v>1967</v>
@@ -25206,7 +25206,7 @@
         <v>14</v>
       </c>
       <c r="E359">
-        <v>0.36098399999999997</v>
+        <v>0.37181351999999995</v>
       </c>
       <c r="F359">
         <v>1726</v>
@@ -25241,7 +25241,7 @@
         <v>14</v>
       </c>
       <c r="E360">
-        <v>0.36098399999999997</v>
+        <v>0.37181351999999995</v>
       </c>
       <c r="F360">
         <v>1726</v>
@@ -27161,7 +27161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{544B47F1-1D70-43DF-B8AA-F0D183D42046}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03C7AF13-6177-43E6-A78A-D7CF0EC70912}">
   <dimension ref="B9:T905"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27246,7 +27246,7 @@
         <v>0.04</v>
       </c>
       <c r="G11">
-        <v>0.24479999999999999</v>
+        <v>0.25214399999999998</v>
       </c>
       <c r="H11">
         <v>3307.5</v>
@@ -27299,7 +27299,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="G12">
-        <v>0.26880000000000004</v>
+        <v>0.27686400000000005</v>
       </c>
       <c r="H12">
         <v>3307.5</v>
@@ -27352,7 +27352,7 @@
         <v>3.1E-2</v>
       </c>
       <c r="G13">
-        <v>0.26880000000000004</v>
+        <v>0.27686400000000005</v>
       </c>
       <c r="H13">
         <v>3307.5</v>
@@ -27405,7 +27405,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="G14">
-        <v>0.26880000000000004</v>
+        <v>0.27686400000000005</v>
       </c>
       <c r="H14">
         <v>3307.5</v>
@@ -27458,7 +27458,7 @@
         <v>0.03</v>
       </c>
       <c r="G15">
-        <v>0.26880000000000004</v>
+        <v>0.27686400000000005</v>
       </c>
       <c r="H15">
         <v>3307.5</v>
@@ -27511,7 +27511,7 @@
         <v>0.115</v>
       </c>
       <c r="G16">
-        <v>0.28799999999999998</v>
+        <v>0.29663999999999996</v>
       </c>
       <c r="H16">
         <v>3307.5</v>
@@ -27564,7 +27564,7 @@
         <v>0.08</v>
       </c>
       <c r="G17">
-        <v>0.28799999999999998</v>
+        <v>0.29663999999999996</v>
       </c>
       <c r="H17">
         <v>3307.5</v>
@@ -27617,7 +27617,7 @@
         <v>0.107</v>
       </c>
       <c r="G18">
-        <v>0.28799999999999998</v>
+        <v>0.29663999999999996</v>
       </c>
       <c r="H18">
         <v>3307.5</v>
@@ -27670,7 +27670,7 @@
         <v>0.03</v>
       </c>
       <c r="G19">
-        <v>0.28799999999999998</v>
+        <v>0.29663999999999996</v>
       </c>
       <c r="H19">
         <v>3307.5</v>
@@ -27723,7 +27723,7 @@
         <v>9.73</v>
       </c>
       <c r="G20">
-        <v>0.33599999999999997</v>
+        <v>0.34608</v>
       </c>
       <c r="H20">
         <v>2450</v>
@@ -27776,7 +27776,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="G21">
-        <v>0.25440000000000002</v>
+        <v>0.26203200000000004</v>
       </c>
       <c r="H21">
         <v>2817.4999999999995</v>
@@ -27829,7 +27829,7 @@
         <v>0.05</v>
       </c>
       <c r="G22">
-        <v>0.28799999999999998</v>
+        <v>0.29663999999999996</v>
       </c>
       <c r="H22">
         <v>3307.5</v>
@@ -27882,7 +27882,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="G23">
-        <v>0.29759999999999998</v>
+        <v>0.30652799999999997</v>
       </c>
       <c r="H23">
         <v>2817.4999999999995</v>
@@ -27935,7 +27935,7 @@
         <v>0.25</v>
       </c>
       <c r="G24">
-        <v>0.34079999999999999</v>
+        <v>0.351024</v>
       </c>
       <c r="H24">
         <v>1851.4999999999998</v>
@@ -27988,7 +27988,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="G25">
-        <v>0.33726315789473682</v>
+        <v>0.34738105263157892</v>
       </c>
       <c r="H25">
         <v>1970.1315789473683</v>
@@ -28041,7 +28041,7 @@
         <v>6.3E-2</v>
       </c>
       <c r="G26">
-        <v>0.34079999999999999</v>
+        <v>0.351024</v>
       </c>
       <c r="H26">
         <v>1851.4999999999998</v>
@@ -28094,7 +28094,7 @@
         <v>0.25</v>
       </c>
       <c r="G27">
-        <v>0.34079999999999999</v>
+        <v>0.351024</v>
       </c>
       <c r="H27">
         <v>1851.4999999999998</v>
@@ -28147,7 +28147,7 @@
         <v>0.28499999999999998</v>
       </c>
       <c r="G28">
-        <v>0.33962105263157893</v>
+        <v>0.34980968421052627</v>
       </c>
       <c r="H28">
         <v>1891.0438596491229</v>
@@ -28200,7 +28200,7 @@
         <v>0.25</v>
       </c>
       <c r="G29">
-        <v>0.34079999999999999</v>
+        <v>0.351024</v>
       </c>
       <c r="H29">
         <v>1851.4999999999998</v>
@@ -28253,7 +28253,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="G30">
-        <v>0.35039999999999999</v>
+        <v>0.36091200000000001</v>
       </c>
       <c r="H30">
         <v>1851.4999999999998</v>
@@ -28306,7 +28306,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="G31">
-        <v>0.35039999999999999</v>
+        <v>0.36091200000000001</v>
       </c>
       <c r="H31">
         <v>1851.4999999999998</v>
@@ -28359,7 +28359,7 @@
         <v>0.3</v>
       </c>
       <c r="G32">
-        <v>0.34079999999999999</v>
+        <v>0.351024</v>
       </c>
       <c r="H32">
         <v>1851.4999999999995</v>
@@ -28412,7 +28412,7 @@
         <v>0.09</v>
       </c>
       <c r="G33">
-        <v>0.2848</v>
+        <v>0.29334399999999999</v>
       </c>
       <c r="H33">
         <v>1703.3333333333333</v>
@@ -28465,7 +28465,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
       <c r="G34">
-        <v>0.28799999999999998</v>
+        <v>0.29663999999999996</v>
       </c>
       <c r="H34">
         <v>1610</v>
@@ -28518,7 +28518,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
       <c r="G35">
-        <v>0.28799999999999998</v>
+        <v>0.29663999999999996</v>
       </c>
       <c r="H35">
         <v>1610</v>
@@ -28571,7 +28571,7 @@
         <v>5.5E-2</v>
       </c>
       <c r="G36">
-        <v>0.30719999999999997</v>
+        <v>0.31641599999999998</v>
       </c>
       <c r="H36">
         <v>1610</v>
@@ -28624,7 +28624,7 @@
         <v>5.5E-2</v>
       </c>
       <c r="G37">
-        <v>0.30719999999999997</v>
+        <v>0.31641599999999998</v>
       </c>
       <c r="H37">
         <v>1610</v>
@@ -28677,7 +28677,7 @@
         <v>0.2</v>
       </c>
       <c r="G38">
-        <v>0.30719999999999997</v>
+        <v>0.31641599999999998</v>
       </c>
       <c r="H38">
         <v>1610</v>
@@ -28730,7 +28730,7 @@
         <v>0.11</v>
       </c>
       <c r="G39">
-        <v>0.30719999999999997</v>
+        <v>0.31641599999999998</v>
       </c>
       <c r="H39">
         <v>1610</v>
@@ -28783,7 +28783,7 @@
         <v>1.55</v>
       </c>
       <c r="G40">
-        <v>0.30720000000000003</v>
+        <v>0.31641599999999992</v>
       </c>
       <c r="H40">
         <v>1610</v>
@@ -28836,7 +28836,7 @@
         <v>1.0024999999999999</v>
       </c>
       <c r="G41">
-        <v>0.30719999999999997</v>
+        <v>0.31641599999999998</v>
       </c>
       <c r="H41">
         <v>1610</v>
@@ -28889,7 +28889,7 @@
         <v>0.48399999999999999</v>
       </c>
       <c r="G42">
-        <v>0.31679999999999997</v>
+        <v>0.32630400000000009</v>
       </c>
       <c r="H42">
         <v>1610</v>
@@ -28942,7 +28942,7 @@
         <v>1.88</v>
       </c>
       <c r="G43">
-        <v>0.31664680851063831</v>
+        <v>0.32614621276595746</v>
       </c>
       <c r="H43">
         <v>1614.4680851063829</v>
@@ -28995,7 +28995,7 @@
         <v>2.0739999999999998</v>
       </c>
       <c r="G44">
-        <v>0.31666113789778216</v>
+        <v>0.32616097203471561</v>
       </c>
       <c r="H44">
         <v>1614.0501446480232</v>
@@ -29048,7 +29048,7 @@
         <v>1.7</v>
       </c>
       <c r="G45">
-        <v>0.31680000000000003</v>
+        <v>0.32630400000000009</v>
       </c>
       <c r="H45">
         <v>1610</v>
@@ -29101,7 +29101,7 @@
         <v>1.5609999999999999</v>
       </c>
       <c r="G46">
-        <v>0.31643100576553501</v>
+        <v>0.32592393593850094</v>
       </c>
       <c r="H46">
         <v>1620.7623318385649</v>
@@ -29154,7 +29154,7 @@
         <v>2.14</v>
       </c>
       <c r="G47">
-        <v>0.31680000000000003</v>
+        <v>0.32630400000000004</v>
       </c>
       <c r="H47">
         <v>1610</v>
@@ -29207,7 +29207,7 @@
         <v>1.58</v>
       </c>
       <c r="G48">
-        <v>0.31680000000000008</v>
+        <v>0.32630400000000004</v>
       </c>
       <c r="H48">
         <v>1610</v>
@@ -29260,7 +29260,7 @@
         <v>1.839</v>
       </c>
       <c r="G49">
-        <v>0.31680000000000003</v>
+        <v>0.32630399999999998</v>
       </c>
       <c r="H49">
         <v>1610</v>
@@ -29313,7 +29313,7 @@
         <v>2.0379999999999998</v>
       </c>
       <c r="G50">
-        <v>0.31680000000000008</v>
+        <v>0.32630400000000015</v>
       </c>
       <c r="H50">
         <v>1610</v>
@@ -29366,7 +29366,7 @@
         <v>1.7050000000000001</v>
       </c>
       <c r="G51">
-        <v>0.31663108504398835</v>
+        <v>0.32613001759530802</v>
       </c>
       <c r="H51">
         <v>1614.9266862170089</v>
@@ -29419,7 +29419,7 @@
         <v>1.55</v>
       </c>
       <c r="G52">
-        <v>0.32584258064516131</v>
+        <v>0.33561785806451622</v>
       </c>
       <c r="H52">
         <v>1626.258064516129</v>
@@ -29472,7 +29472,7 @@
         <v>1.05</v>
       </c>
       <c r="G53">
-        <v>0.32640000000000002</v>
+        <v>0.33619200000000005</v>
       </c>
       <c r="H53">
         <v>1610</v>
@@ -29525,7 +29525,7 @@
         <v>0.84</v>
       </c>
       <c r="G54">
-        <v>0.32640000000000008</v>
+        <v>0.33619200000000005</v>
       </c>
       <c r="H54">
         <v>1610</v>
@@ -29578,7 +29578,7 @@
         <v>1.8674999999999999</v>
       </c>
       <c r="G55">
-        <v>0.32640000000000002</v>
+        <v>0.3361920000000001</v>
       </c>
       <c r="H55">
         <v>1610</v>
@@ -29631,7 +29631,7 @@
         <v>1.97</v>
       </c>
       <c r="G56">
-        <v>0.32639999999999997</v>
+        <v>0.33619200000000005</v>
       </c>
       <c r="H56">
         <v>1610</v>
@@ -29684,7 +29684,7 @@
         <v>1.0049999999999999</v>
       </c>
       <c r="G57">
-        <v>0.32611343283582089</v>
+        <v>0.33589683582089558</v>
       </c>
       <c r="H57">
         <v>1618.358208955224</v>
@@ -29737,7 +29737,7 @@
         <v>1.3089999999999999</v>
       </c>
       <c r="G58">
-        <v>0.32617998472116122</v>
+        <v>0.3359653842627961</v>
       </c>
       <c r="H58">
         <v>1616.4171122994653</v>
@@ -29790,7 +29790,7 @@
         <v>1.6307</v>
       </c>
       <c r="G59">
-        <v>0.32622338872876688</v>
+        <v>0.33601009039062985</v>
       </c>
       <c r="H59">
         <v>1615.1511620776353</v>
@@ -29843,7 +29843,7 @@
         <v>2.2450000000000001</v>
       </c>
       <c r="G60">
-        <v>0.32605790645879734</v>
+        <v>0.33583964365256125</v>
       </c>
       <c r="H60">
         <v>1619.977728285078</v>
@@ -29896,7 +29896,7 @@
         <v>1.2050000000000001</v>
       </c>
       <c r="G61">
-        <v>0.32616099585062247</v>
+        <v>0.33594582572614112</v>
       </c>
       <c r="H61">
         <v>1616.9709543568465</v>
@@ -29949,7 +29949,7 @@
         <v>1.0549999999999999</v>
       </c>
       <c r="G62">
-        <v>0.32640000000000008</v>
+        <v>0.33619200000000005</v>
       </c>
       <c r="H62">
         <v>1610</v>
@@ -30002,7 +30002,7 @@
         <v>1.04</v>
       </c>
       <c r="G63">
-        <v>0.32640000000000002</v>
+        <v>0.33619200000000005</v>
       </c>
       <c r="H63">
         <v>1610</v>
@@ -30055,7 +30055,7 @@
         <v>0.64300000000000002</v>
       </c>
       <c r="G64">
-        <v>0.32590730948678076</v>
+        <v>0.33568452877138422</v>
       </c>
       <c r="H64">
         <v>1624.3701399688957</v>
@@ -30108,7 +30108,7 @@
         <v>0.53749999999999998</v>
       </c>
       <c r="G65">
-        <v>0.32573023255813954</v>
+        <v>0.33550213953488384</v>
       </c>
       <c r="H65">
         <v>1629.5348837209303</v>
@@ -30161,7 +30161,7 @@
         <v>1.325</v>
       </c>
       <c r="G66">
-        <v>0.32582037735849062</v>
+        <v>0.33559498867924531</v>
       </c>
       <c r="H66">
         <v>1626.9056603773586</v>
@@ -30214,7 +30214,7 @@
         <v>1.288</v>
       </c>
       <c r="G67">
-        <v>0.32502857142857144</v>
+        <v>0.33477942857142867</v>
       </c>
       <c r="H67">
         <v>1650</v>
@@ -30267,7 +30267,7 @@
         <v>3.238</v>
       </c>
       <c r="G68">
-        <v>0.32578332303891294</v>
+        <v>0.33555682273008036</v>
       </c>
       <c r="H68">
         <v>1627.9864113650401</v>
@@ -30320,7 +30320,7 @@
         <v>4.3159999999999998</v>
       </c>
       <c r="G69">
-        <v>0.32586394810009262</v>
+        <v>0.33563986654309558</v>
       </c>
       <c r="H69">
         <v>1625.6348470806302</v>
@@ -30373,7 +30373,7 @@
         <v>4.6105</v>
       </c>
       <c r="G70">
-        <v>0.32747649929508732</v>
+        <v>0.33730079427394</v>
       </c>
       <c r="H70">
         <v>1603.6536167443878</v>
@@ -30426,7 +30426,7 @@
         <v>6.524</v>
       </c>
       <c r="G71">
-        <v>0.33187835683629674</v>
+        <v>0.34183470754138578</v>
       </c>
       <c r="H71">
         <v>1555.901287553648</v>
@@ -30479,7 +30479,7 @@
         <v>4.4800000000000004</v>
       </c>
       <c r="G72">
-        <v>0.32524071428571433</v>
+        <v>0.33499793571428566</v>
       </c>
       <c r="H72">
         <v>1643.8125</v>
@@ -30532,7 +30532,7 @@
         <v>4.4409999999999998</v>
       </c>
       <c r="G73">
-        <v>0.32501652780905205</v>
+        <v>0.33476702364332367</v>
       </c>
       <c r="H73">
         <v>1650.3512722359828</v>
@@ -30585,7 +30585,7 @@
         <v>7.6130000000000004</v>
       </c>
       <c r="G74">
-        <v>0.32790689609877854</v>
+        <v>0.33774410298174184</v>
       </c>
       <c r="H74">
         <v>1598.2306580848549</v>
@@ -30638,7 +30638,7 @@
         <v>3.3759999999999999</v>
       </c>
       <c r="G75">
-        <v>0.32781895734597155</v>
+        <v>0.33765352606635063</v>
       </c>
       <c r="H75">
         <v>1604.899289099526</v>
@@ -30691,7 +30691,7 @@
         <v>4.2699999999999996</v>
       </c>
       <c r="G76">
-        <v>0.32781639344262292</v>
+        <v>0.33765088524590164</v>
       </c>
       <c r="H76">
         <v>1598.1967213114754</v>
@@ -30744,7 +30744,7 @@
         <v>3.06</v>
       </c>
       <c r="G77">
-        <v>0.33060392156862745</v>
+        <v>0.3405220392156863</v>
       </c>
       <c r="H77">
         <v>1568.5947712418301</v>
@@ -30797,7 +30797,7 @@
         <v>3.3719999999999999</v>
       </c>
       <c r="G78">
-        <v>0.32825907473309612</v>
+        <v>0.33810684697508903</v>
       </c>
       <c r="H78">
         <v>1593.1435349940689</v>
@@ -30850,7 +30850,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G79">
-        <v>0.32640000000000002</v>
+        <v>0.3361920000000001</v>
       </c>
       <c r="H79">
         <v>1610</v>
@@ -30903,7 +30903,7 @@
         <v>1.0549999999999999</v>
       </c>
       <c r="G80">
-        <v>0.3325421800947867</v>
+        <v>0.34251844549763039</v>
       </c>
       <c r="H80">
         <v>1550.2843601895734</v>
@@ -30956,7 +30956,7 @@
         <v>0.54</v>
       </c>
       <c r="G81">
-        <v>0.32640000000000002</v>
+        <v>0.33619200000000005</v>
       </c>
       <c r="H81">
         <v>1610</v>
@@ -31009,7 +31009,7 @@
         <v>0.87</v>
       </c>
       <c r="G82">
-        <v>0.3260689655172414</v>
+        <v>0.33585103448275866</v>
       </c>
       <c r="H82">
         <v>1619.655172413793</v>
@@ -31062,7 +31062,7 @@
         <v>0.95079999999997422</v>
       </c>
       <c r="G83">
-        <v>0.33328195204038669</v>
+        <v>0.34328041060159831</v>
       </c>
       <c r="H83">
         <v>1545.7719814892762</v>
@@ -31115,7 +31115,7 @@
         <v>0.15</v>
       </c>
       <c r="G84">
-        <v>0.32640000000000002</v>
+        <v>0.33619200000000005</v>
       </c>
       <c r="H84">
         <v>1610</v>
@@ -31168,7 +31168,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="G85">
-        <v>0.33616551724137933</v>
+        <v>0.34625048275862064</v>
       </c>
       <c r="H85">
         <v>1536.3793103448277</v>
@@ -31221,7 +31221,7 @@
         <v>0.7</v>
       </c>
       <c r="G86">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H86">
         <v>1400</v>
@@ -31274,7 +31274,7 @@
         <v>0.6</v>
       </c>
       <c r="G87">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H87">
         <v>1400</v>
@@ -31327,7 +31327,7 @@
         <v>0.6</v>
       </c>
       <c r="G88">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H88">
         <v>1400</v>
@@ -31380,7 +31380,7 @@
         <v>0.6</v>
       </c>
       <c r="G89">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H89">
         <v>1400</v>
@@ -31433,7 +31433,7 @@
         <v>0.5</v>
       </c>
       <c r="G90">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H90">
         <v>1400</v>
@@ -31486,7 +31486,7 @@
         <v>0.5</v>
       </c>
       <c r="G91">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H91">
         <v>1400</v>
@@ -31539,7 +31539,7 @@
         <v>0.6</v>
       </c>
       <c r="G92">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H92">
         <v>1400</v>
@@ -31592,7 +31592,7 @@
         <v>0.6</v>
       </c>
       <c r="G93">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H93">
         <v>1400</v>
@@ -31645,7 +31645,7 @@
         <v>0.5</v>
       </c>
       <c r="G94">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H94">
         <v>1400</v>
@@ -31698,7 +31698,7 @@
         <v>0.5</v>
       </c>
       <c r="G95">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H95">
         <v>1400</v>
@@ -31751,7 +31751,7 @@
         <v>0.63</v>
       </c>
       <c r="G96">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H96">
         <v>1400</v>
@@ -31804,7 +31804,7 @@
         <v>0.63</v>
       </c>
       <c r="G97">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H97">
         <v>1400</v>
@@ -31857,7 +31857,7 @@
         <v>0.6</v>
       </c>
       <c r="G98">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H98">
         <v>1400</v>
@@ -31910,7 +31910,7 @@
         <v>0.6</v>
       </c>
       <c r="G99">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H99">
         <v>1400</v>
@@ -31963,7 +31963,7 @@
         <v>0.5</v>
       </c>
       <c r="G100">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H100">
         <v>1400</v>
@@ -32016,7 +32016,7 @@
         <v>0.5</v>
       </c>
       <c r="G101">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H101">
         <v>1400</v>
@@ -32069,7 +32069,7 @@
         <v>0.5</v>
       </c>
       <c r="G102">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H102">
         <v>1400</v>
@@ -32122,7 +32122,7 @@
         <v>0.5</v>
       </c>
       <c r="G103">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H103">
         <v>1400</v>
@@ -32175,7 +32175,7 @@
         <v>0.5</v>
       </c>
       <c r="G104">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H104">
         <v>1400</v>
@@ -32228,7 +32228,7 @@
         <v>0.5</v>
       </c>
       <c r="G105">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H105">
         <v>1400</v>
@@ -32281,7 +32281,7 @@
         <v>0.5</v>
       </c>
       <c r="G106">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H106">
         <v>1400</v>
@@ -32334,7 +32334,7 @@
         <v>0.5</v>
       </c>
       <c r="G107">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H107">
         <v>1400</v>
@@ -32387,7 +32387,7 @@
         <v>0.5</v>
       </c>
       <c r="G108">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H108">
         <v>1400</v>
@@ -32440,7 +32440,7 @@
         <v>0.5</v>
       </c>
       <c r="G109">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H109">
         <v>1400</v>
@@ -32493,7 +32493,7 @@
         <v>0.5</v>
       </c>
       <c r="G110">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H110">
         <v>1400</v>
@@ -32546,7 +32546,7 @@
         <v>0.5</v>
       </c>
       <c r="G111">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H111">
         <v>1400</v>
@@ -32599,7 +32599,7 @@
         <v>0.5</v>
       </c>
       <c r="G112">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H112">
         <v>1400</v>
@@ -32652,7 +32652,7 @@
         <v>0.5</v>
       </c>
       <c r="G113">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H113">
         <v>1400</v>
@@ -32705,7 +32705,7 @@
         <v>0.5</v>
       </c>
       <c r="G114">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H114">
         <v>1400</v>
@@ -32758,7 +32758,7 @@
         <v>0.5</v>
       </c>
       <c r="G115">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H115">
         <v>1400</v>
@@ -32811,7 +32811,7 @@
         <v>0.5</v>
       </c>
       <c r="G116">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H116">
         <v>1400</v>
@@ -32864,7 +32864,7 @@
         <v>0.8</v>
       </c>
       <c r="G117">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H117">
         <v>1400</v>
@@ -32917,7 +32917,7 @@
         <v>0.8</v>
       </c>
       <c r="G118">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H118">
         <v>1400</v>
@@ -32970,7 +32970,7 @@
         <v>0.5</v>
       </c>
       <c r="G119">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H119">
         <v>1400</v>
@@ -33023,7 +33023,7 @@
         <v>0.5</v>
       </c>
       <c r="G120">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H120">
         <v>1400</v>
@@ -33076,7 +33076,7 @@
         <v>0.5</v>
       </c>
       <c r="G121">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H121">
         <v>1400</v>
@@ -33129,7 +33129,7 @@
         <v>0.5</v>
       </c>
       <c r="G122">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H122">
         <v>1400</v>
@@ -33182,7 +33182,7 @@
         <v>0.6</v>
       </c>
       <c r="G123">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H123">
         <v>1400</v>
@@ -33235,7 +33235,7 @@
         <v>0.6</v>
       </c>
       <c r="G124">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H124">
         <v>1400</v>
@@ -33288,7 +33288,7 @@
         <v>0.6</v>
       </c>
       <c r="G125">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H125">
         <v>1400</v>
@@ -33341,7 +33341,7 @@
         <v>0.6</v>
       </c>
       <c r="G126">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H126">
         <v>1400</v>
@@ -33394,7 +33394,7 @@
         <v>0.6</v>
       </c>
       <c r="G127">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H127">
         <v>1400</v>
@@ -33447,7 +33447,7 @@
         <v>0.5</v>
       </c>
       <c r="G128">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H128">
         <v>1400</v>
@@ -33500,7 +33500,7 @@
         <v>0.5</v>
       </c>
       <c r="G129">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H129">
         <v>1400</v>
@@ -33553,7 +33553,7 @@
         <v>0.5</v>
       </c>
       <c r="G130">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H130">
         <v>1400</v>
@@ -33606,7 +33606,7 @@
         <v>0.5</v>
       </c>
       <c r="G131">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H131">
         <v>1400</v>
@@ -33659,7 +33659,7 @@
         <v>0.6</v>
       </c>
       <c r="G132">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H132">
         <v>1400</v>
@@ -33712,7 +33712,7 @@
         <v>0.5</v>
       </c>
       <c r="G133">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H133">
         <v>1400</v>
@@ -33765,7 +33765,7 @@
         <v>0.5</v>
       </c>
       <c r="G134">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H134">
         <v>1400</v>
@@ -33818,7 +33818,7 @@
         <v>0.5</v>
       </c>
       <c r="G135">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H135">
         <v>1400</v>
@@ -33871,7 +33871,7 @@
         <v>0.5</v>
       </c>
       <c r="G136">
-        <v>0.33599999999999997</v>
+        <v>0.34608</v>
       </c>
       <c r="H136">
         <v>1400</v>
@@ -33924,7 +33924,7 @@
         <v>0.5</v>
       </c>
       <c r="G137">
-        <v>0.33599999999999997</v>
+        <v>0.34608</v>
       </c>
       <c r="H137">
         <v>1400</v>
@@ -33977,7 +33977,7 @@
         <v>0.5</v>
       </c>
       <c r="G138">
-        <v>0.33599999999999997</v>
+        <v>0.34608</v>
       </c>
       <c r="H138">
         <v>1400</v>
@@ -34030,7 +34030,7 @@
         <v>0.5</v>
       </c>
       <c r="G139">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H139">
         <v>1400</v>
@@ -34083,7 +34083,7 @@
         <v>0.66</v>
       </c>
       <c r="G140">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H140">
         <v>1400</v>
@@ -34136,7 +34136,7 @@
         <v>0.66</v>
       </c>
       <c r="G141">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H141">
         <v>1400</v>
@@ -34189,7 +34189,7 @@
         <v>0.6</v>
       </c>
       <c r="G142">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H142">
         <v>1400</v>
@@ -34242,7 +34242,7 @@
         <v>0.6</v>
       </c>
       <c r="G143">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H143">
         <v>1400</v>
@@ -34295,7 +34295,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="G144">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H144">
         <v>1400</v>
@@ -34348,7 +34348,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="G145">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H145">
         <v>1400</v>
@@ -34401,7 +34401,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="G146">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H146">
         <v>1400</v>
@@ -34454,7 +34454,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="G147">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H147">
         <v>1400</v>
@@ -34507,7 +34507,7 @@
         <v>0.5</v>
       </c>
       <c r="G148">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H148">
         <v>1400</v>
@@ -34560,7 +34560,7 @@
         <v>0.5</v>
       </c>
       <c r="G149">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H149">
         <v>1400</v>
@@ -34613,7 +34613,7 @@
         <v>0.5</v>
       </c>
       <c r="G150">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H150">
         <v>1400</v>
@@ -34666,7 +34666,7 @@
         <v>0.5</v>
       </c>
       <c r="G151">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H151">
         <v>1400</v>
@@ -34719,7 +34719,7 @@
         <v>0.5</v>
       </c>
       <c r="G152">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H152">
         <v>1400</v>
@@ -34772,7 +34772,7 @@
         <v>0.5</v>
       </c>
       <c r="G153">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H153">
         <v>1400</v>
@@ -34825,7 +34825,7 @@
         <v>0.6</v>
       </c>
       <c r="G154">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H154">
         <v>1400</v>
@@ -34878,7 +34878,7 @@
         <v>0.6</v>
       </c>
       <c r="G155">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H155">
         <v>1400</v>
@@ -34931,7 +34931,7 @@
         <v>0.5</v>
       </c>
       <c r="G156">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H156">
         <v>1400</v>
@@ -34984,7 +34984,7 @@
         <v>0.5</v>
       </c>
       <c r="G157">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H157">
         <v>1400</v>
@@ -35037,7 +35037,7 @@
         <v>0.6</v>
       </c>
       <c r="G158">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H158">
         <v>1400</v>
@@ -35090,7 +35090,7 @@
         <v>0.6</v>
       </c>
       <c r="G159">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H159">
         <v>1400</v>
@@ -35143,7 +35143,7 @@
         <v>0.6</v>
       </c>
       <c r="G160">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H160">
         <v>1400</v>
@@ -35196,7 +35196,7 @@
         <v>0.6</v>
       </c>
       <c r="G161">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H161">
         <v>1400</v>
@@ -35249,7 +35249,7 @@
         <v>0.6</v>
       </c>
       <c r="G162">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H162">
         <v>1400</v>
@@ -35302,7 +35302,7 @@
         <v>0.6</v>
       </c>
       <c r="G163">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H163">
         <v>1400</v>
@@ -35355,7 +35355,7 @@
         <v>0.5</v>
       </c>
       <c r="G164">
-        <v>0.33599999999999997</v>
+        <v>0.34608</v>
       </c>
       <c r="H164">
         <v>1400</v>
@@ -35408,7 +35408,7 @@
         <v>0.5</v>
       </c>
       <c r="G165">
-        <v>0.33599999999999997</v>
+        <v>0.34608</v>
       </c>
       <c r="H165">
         <v>1400</v>
@@ -35461,7 +35461,7 @@
         <v>0.5</v>
       </c>
       <c r="G166">
-        <v>0.33599999999999997</v>
+        <v>0.34608</v>
       </c>
       <c r="H166">
         <v>1400</v>
@@ -35514,7 +35514,7 @@
         <v>0.5</v>
       </c>
       <c r="G167">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H167">
         <v>1400</v>
@@ -35567,7 +35567,7 @@
         <v>0.6</v>
       </c>
       <c r="G168">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H168">
         <v>1400</v>
@@ -35620,7 +35620,7 @@
         <v>0.5</v>
       </c>
       <c r="G169">
-        <v>0.33599999999999997</v>
+        <v>0.34608</v>
       </c>
       <c r="H169">
         <v>1400</v>
@@ -35673,7 +35673,7 @@
         <v>0.5</v>
       </c>
       <c r="G170">
-        <v>0.33599999999999997</v>
+        <v>0.34608</v>
       </c>
       <c r="H170">
         <v>1400</v>
@@ -35726,7 +35726,7 @@
         <v>0.5</v>
       </c>
       <c r="G171">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H171">
         <v>1400</v>
@@ -35779,7 +35779,7 @@
         <v>0.5</v>
       </c>
       <c r="G172">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H172">
         <v>1400</v>
@@ -35832,7 +35832,7 @@
         <v>0.5</v>
       </c>
       <c r="G173">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H173">
         <v>1400</v>
@@ -35885,7 +35885,7 @@
         <v>0.5</v>
       </c>
       <c r="G174">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H174">
         <v>1400</v>
@@ -35938,7 +35938,7 @@
         <v>0.5</v>
       </c>
       <c r="G175">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H175">
         <v>1400</v>
@@ -35991,7 +35991,7 @@
         <v>0.5</v>
       </c>
       <c r="G176">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H176">
         <v>1400</v>
@@ -36044,7 +36044,7 @@
         <v>0.6</v>
       </c>
       <c r="G177">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H177">
         <v>1400</v>
@@ -36097,7 +36097,7 @@
         <v>0.6</v>
       </c>
       <c r="G178">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H178">
         <v>1400</v>
@@ -36150,7 +36150,7 @@
         <v>0.5</v>
       </c>
       <c r="G179">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H179">
         <v>1400</v>
@@ -36203,7 +36203,7 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="G180">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H180">
         <v>1400</v>
@@ -36256,7 +36256,7 @@
         <v>0.6</v>
       </c>
       <c r="G181">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H181">
         <v>1400</v>
@@ -36309,7 +36309,7 @@
         <v>0.6</v>
       </c>
       <c r="G182">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H182">
         <v>1400</v>
@@ -36362,7 +36362,7 @@
         <v>0.5</v>
       </c>
       <c r="G183">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H183">
         <v>1400</v>
@@ -36415,7 +36415,7 @@
         <v>0.5</v>
       </c>
       <c r="G184">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H184">
         <v>1400</v>
@@ -36468,7 +36468,7 @@
         <v>0.5</v>
       </c>
       <c r="G185">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H185">
         <v>1400</v>
@@ -36521,7 +36521,7 @@
         <v>0.5</v>
       </c>
       <c r="G186">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H186">
         <v>1400</v>
@@ -36574,7 +36574,7 @@
         <v>0.5</v>
       </c>
       <c r="G187">
-        <v>0.33599999999999997</v>
+        <v>0.34608</v>
       </c>
       <c r="H187">
         <v>1400</v>
@@ -36627,7 +36627,7 @@
         <v>0.5</v>
       </c>
       <c r="G188">
-        <v>0.33599999999999997</v>
+        <v>0.34608</v>
       </c>
       <c r="H188">
         <v>1400</v>
@@ -36680,7 +36680,7 @@
         <v>0.5</v>
       </c>
       <c r="G189">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H189">
         <v>1400</v>
@@ -36733,7 +36733,7 @@
         <v>0.5</v>
       </c>
       <c r="G190">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H190">
         <v>1400</v>
@@ -36786,7 +36786,7 @@
         <v>0.5</v>
       </c>
       <c r="G191">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H191">
         <v>1400</v>
@@ -36839,7 +36839,7 @@
         <v>0.5</v>
       </c>
       <c r="G192">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H192">
         <v>1400</v>
@@ -36892,7 +36892,7 @@
         <v>0.5</v>
       </c>
       <c r="G193">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H193">
         <v>1400</v>
@@ -36945,7 +36945,7 @@
         <v>0.5</v>
       </c>
       <c r="G194">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H194">
         <v>1400</v>
@@ -36998,7 +36998,7 @@
         <v>0.5</v>
       </c>
       <c r="G195">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H195">
         <v>1400</v>
@@ -37051,7 +37051,7 @@
         <v>0.5</v>
       </c>
       <c r="G196">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H196">
         <v>1400</v>
@@ -37104,7 +37104,7 @@
         <v>0.6</v>
       </c>
       <c r="G197">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H197">
         <v>1400</v>
@@ -37157,7 +37157,7 @@
         <v>0.6</v>
       </c>
       <c r="G198">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H198">
         <v>1400</v>
@@ -37210,7 +37210,7 @@
         <v>0.6</v>
       </c>
       <c r="G199">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H199">
         <v>1400</v>
@@ -37263,7 +37263,7 @@
         <v>0.6</v>
       </c>
       <c r="G200">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H200">
         <v>1400</v>
@@ -37316,7 +37316,7 @@
         <v>0.5</v>
       </c>
       <c r="G201">
-        <v>0.33599999999999997</v>
+        <v>0.34608</v>
       </c>
       <c r="H201">
         <v>1400</v>
@@ -37369,7 +37369,7 @@
         <v>0.5</v>
       </c>
       <c r="G202">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H202">
         <v>1400</v>
@@ -37422,7 +37422,7 @@
         <v>0.5</v>
       </c>
       <c r="G203">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H203">
         <v>1400</v>
@@ -37475,7 +37475,7 @@
         <v>0.5</v>
       </c>
       <c r="G204">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H204">
         <v>1400</v>
@@ -37528,7 +37528,7 @@
         <v>0.5</v>
       </c>
       <c r="G205">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H205">
         <v>1400</v>
@@ -37581,7 +37581,7 @@
         <v>0.5</v>
       </c>
       <c r="G206">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H206">
         <v>1400</v>
@@ -37634,7 +37634,7 @@
         <v>0.5</v>
       </c>
       <c r="G207">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H207">
         <v>1400</v>
@@ -37687,7 +37687,7 @@
         <v>0.5</v>
       </c>
       <c r="G208">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H208">
         <v>1400</v>
@@ -37740,7 +37740,7 @@
         <v>0.5</v>
       </c>
       <c r="G209">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H209">
         <v>1400</v>
@@ -37793,7 +37793,7 @@
         <v>0.5</v>
       </c>
       <c r="G210">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H210">
         <v>1400</v>
@@ -37846,7 +37846,7 @@
         <v>0.5</v>
       </c>
       <c r="G211">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H211">
         <v>1400</v>
@@ -37899,7 +37899,7 @@
         <v>0.5</v>
       </c>
       <c r="G212">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H212">
         <v>1400</v>
@@ -37952,7 +37952,7 @@
         <v>0.5</v>
       </c>
       <c r="G213">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H213">
         <v>1400</v>
@@ -38005,7 +38005,7 @@
         <v>0.5</v>
       </c>
       <c r="G214">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H214">
         <v>1400</v>
@@ -38058,7 +38058,7 @@
         <v>0.52</v>
       </c>
       <c r="G215">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H215">
         <v>1400</v>
@@ -38111,7 +38111,7 @@
         <v>0.52</v>
       </c>
       <c r="G216">
-        <v>0.34559999999999996</v>
+        <v>0.35596799999999995</v>
       </c>
       <c r="H216">
         <v>1400</v>
@@ -38164,7 +38164,7 @@
         <v>6.25E-2</v>
       </c>
       <c r="G217">
-        <v>0.30719999999999997</v>
+        <v>0.31641599999999998</v>
       </c>
       <c r="H217">
         <v>1610</v>
@@ -38217,7 +38217,7 @@
         <v>0.03</v>
       </c>
       <c r="G218">
-        <v>0.31680000000000003</v>
+        <v>0.32630400000000004</v>
       </c>
       <c r="H218">
         <v>1889.9999999999998</v>
@@ -38270,7 +38270,7 @@
         <v>0.189</v>
       </c>
       <c r="G219">
-        <v>0.32640000000000002</v>
+        <v>0.33619200000000005</v>
       </c>
       <c r="H219">
         <v>1610</v>
@@ -38323,7 +38323,7 @@
         <v>0.6</v>
       </c>
       <c r="G220">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H220">
         <v>1540</v>
@@ -38376,7 +38376,7 @@
         <v>0.6</v>
       </c>
       <c r="G221">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H221">
         <v>1540</v>
@@ -38429,7 +38429,7 @@
         <v>0.66</v>
       </c>
       <c r="G222">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H222">
         <v>1540</v>
@@ -38482,7 +38482,7 @@
         <v>0.66</v>
       </c>
       <c r="G223">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H223">
         <v>1540</v>
@@ -38535,7 +38535,7 @@
         <v>0.66</v>
       </c>
       <c r="G224">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H224">
         <v>1540</v>
@@ -38588,7 +38588,7 @@
         <v>0.66</v>
       </c>
       <c r="G225">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H225">
         <v>1540</v>
@@ -38641,7 +38641,7 @@
         <v>0.66</v>
       </c>
       <c r="G226">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H226">
         <v>1540</v>
@@ -38694,7 +38694,7 @@
         <v>0.66</v>
       </c>
       <c r="G227">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H227">
         <v>1540</v>
@@ -38747,7 +38747,7 @@
         <v>0.66</v>
       </c>
       <c r="G228">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H228">
         <v>1540</v>
@@ -38800,7 +38800,7 @@
         <v>0.66</v>
       </c>
       <c r="G229">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H229">
         <v>1540</v>
@@ -38853,7 +38853,7 @@
         <v>0.66</v>
       </c>
       <c r="G230">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H230">
         <v>1540</v>
@@ -38906,7 +38906,7 @@
         <v>0.66</v>
       </c>
       <c r="G231">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H231">
         <v>1540</v>
@@ -38959,7 +38959,7 @@
         <v>0.7</v>
       </c>
       <c r="G232">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H232">
         <v>1540</v>
@@ -39012,7 +39012,7 @@
         <v>0.66</v>
       </c>
       <c r="G233">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H233">
         <v>1540</v>
@@ -39065,7 +39065,7 @@
         <v>0.66</v>
       </c>
       <c r="G234">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H234">
         <v>1540</v>
@@ -39118,7 +39118,7 @@
         <v>0.66</v>
       </c>
       <c r="G235">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H235">
         <v>1540</v>
@@ -39171,7 +39171,7 @@
         <v>0.66</v>
       </c>
       <c r="G236">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H236">
         <v>1540</v>
@@ -39224,7 +39224,7 @@
         <v>0.66</v>
       </c>
       <c r="G237">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H237">
         <v>1540</v>
@@ -39277,7 +39277,7 @@
         <v>0.6</v>
       </c>
       <c r="G238">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H238">
         <v>1540</v>
@@ -39330,7 +39330,7 @@
         <v>0.6</v>
       </c>
       <c r="G239">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H239">
         <v>1540</v>
@@ -39383,7 +39383,7 @@
         <v>0.8</v>
       </c>
       <c r="G240">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999994</v>
       </c>
       <c r="H240">
         <v>1540</v>
@@ -39436,7 +39436,7 @@
         <v>0.8</v>
       </c>
       <c r="G241">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H241">
         <v>1540</v>
@@ -39489,7 +39489,7 @@
         <v>0.8</v>
       </c>
       <c r="G242">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H242">
         <v>1540</v>
@@ -39542,7 +39542,7 @@
         <v>0.66</v>
       </c>
       <c r="G243">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H243">
         <v>1540</v>
@@ -39595,7 +39595,7 @@
         <v>0.66</v>
       </c>
       <c r="G244">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H244">
         <v>1540</v>
@@ -39648,7 +39648,7 @@
         <v>0.66</v>
       </c>
       <c r="G245">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H245">
         <v>1540</v>
@@ -39701,7 +39701,7 @@
         <v>0.66</v>
       </c>
       <c r="G246">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H246">
         <v>1540</v>
@@ -39754,7 +39754,7 @@
         <v>0.66</v>
       </c>
       <c r="G247">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H247">
         <v>1540</v>
@@ -39807,7 +39807,7 @@
         <v>0.66</v>
       </c>
       <c r="G248">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H248">
         <v>1540</v>
@@ -39860,7 +39860,7 @@
         <v>0.66</v>
       </c>
       <c r="G249">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H249">
         <v>1540</v>
@@ -39913,7 +39913,7 @@
         <v>0.66</v>
       </c>
       <c r="G250">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H250">
         <v>1540</v>
@@ -39966,7 +39966,7 @@
         <v>0.66</v>
       </c>
       <c r="G251">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H251">
         <v>1540</v>
@@ -40019,7 +40019,7 @@
         <v>0.66</v>
       </c>
       <c r="G252">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H252">
         <v>1540</v>
@@ -40072,7 +40072,7 @@
         <v>0.66</v>
       </c>
       <c r="G253">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H253">
         <v>1540</v>
@@ -40125,7 +40125,7 @@
         <v>0.66</v>
       </c>
       <c r="G254">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H254">
         <v>1540</v>
@@ -40178,7 +40178,7 @@
         <v>0.66</v>
       </c>
       <c r="G255">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H255">
         <v>1540</v>
@@ -40231,7 +40231,7 @@
         <v>0.66</v>
       </c>
       <c r="G256">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H256">
         <v>1540</v>
@@ -40284,7 +40284,7 @@
         <v>0.66</v>
       </c>
       <c r="G257">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H257">
         <v>1540</v>
@@ -40337,7 +40337,7 @@
         <v>0.6</v>
       </c>
       <c r="G258">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H258">
         <v>1540</v>
@@ -40390,7 +40390,7 @@
         <v>0.6</v>
       </c>
       <c r="G259">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H259">
         <v>1540</v>
@@ -40443,7 +40443,7 @@
         <v>0.66</v>
       </c>
       <c r="G260">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H260">
         <v>1540</v>
@@ -40496,7 +40496,7 @@
         <v>0.66</v>
       </c>
       <c r="G261">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H261">
         <v>1540</v>
@@ -40549,7 +40549,7 @@
         <v>0.66</v>
       </c>
       <c r="G262">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H262">
         <v>1540</v>
@@ -40602,7 +40602,7 @@
         <v>0.66</v>
       </c>
       <c r="G263">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H263">
         <v>1540</v>
@@ -40655,7 +40655,7 @@
         <v>0.66</v>
       </c>
       <c r="G264">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H264">
         <v>1540</v>
@@ -40708,7 +40708,7 @@
         <v>0.66</v>
       </c>
       <c r="G265">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H265">
         <v>1540</v>
@@ -40761,7 +40761,7 @@
         <v>0.5</v>
       </c>
       <c r="G266">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H266">
         <v>1540</v>
@@ -40814,7 +40814,7 @@
         <v>0.8</v>
       </c>
       <c r="G267">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999994</v>
       </c>
       <c r="H267">
         <v>1540</v>
@@ -40867,7 +40867,7 @@
         <v>0.6</v>
       </c>
       <c r="G268">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H268">
         <v>1540</v>
@@ -40920,7 +40920,7 @@
         <v>0.6</v>
       </c>
       <c r="G269">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H269">
         <v>1540</v>
@@ -40973,7 +40973,7 @@
         <v>0.6</v>
       </c>
       <c r="G270">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H270">
         <v>1540</v>
@@ -41026,7 +41026,7 @@
         <v>0.6</v>
       </c>
       <c r="G271">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H271">
         <v>1540</v>
@@ -41079,7 +41079,7 @@
         <v>0.6</v>
       </c>
       <c r="G272">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H272">
         <v>1540</v>
@@ -41132,7 +41132,7 @@
         <v>0.6</v>
       </c>
       <c r="G273">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H273">
         <v>1540</v>
@@ -41185,7 +41185,7 @@
         <v>0.8</v>
       </c>
       <c r="G274">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999994</v>
       </c>
       <c r="H274">
         <v>1540</v>
@@ -41238,7 +41238,7 @@
         <v>0.8</v>
       </c>
       <c r="G275">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999994</v>
       </c>
       <c r="H275">
         <v>1540</v>
@@ -41291,7 +41291,7 @@
         <v>0.8</v>
       </c>
       <c r="G276">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999994</v>
       </c>
       <c r="H276">
         <v>1540</v>
@@ -41344,7 +41344,7 @@
         <v>0.66</v>
       </c>
       <c r="G277">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H277">
         <v>1540</v>
@@ -41397,7 +41397,7 @@
         <v>0.66</v>
       </c>
       <c r="G278">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H278">
         <v>1540</v>
@@ -41450,7 +41450,7 @@
         <v>0.66</v>
       </c>
       <c r="G279">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H279">
         <v>1540</v>
@@ -41503,7 +41503,7 @@
         <v>0.8</v>
       </c>
       <c r="G280">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999994</v>
       </c>
       <c r="H280">
         <v>1540</v>
@@ -41556,7 +41556,7 @@
         <v>0.8</v>
       </c>
       <c r="G281">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999994</v>
       </c>
       <c r="H281">
         <v>1540</v>
@@ -41609,7 +41609,7 @@
         <v>0.66</v>
       </c>
       <c r="G282">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H282">
         <v>1540</v>
@@ -41662,7 +41662,7 @@
         <v>0.66</v>
       </c>
       <c r="G283">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H283">
         <v>1540</v>
@@ -41715,7 +41715,7 @@
         <v>0.66</v>
       </c>
       <c r="G284">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H284">
         <v>1540</v>
@@ -41768,7 +41768,7 @@
         <v>0.66</v>
       </c>
       <c r="G285">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H285">
         <v>1540</v>
@@ -41821,7 +41821,7 @@
         <v>0.6</v>
       </c>
       <c r="G286">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H286">
         <v>1540</v>
@@ -41874,7 +41874,7 @@
         <v>0.66</v>
       </c>
       <c r="G287">
-        <v>0.37919999999999998</v>
+        <v>0.39057599999999992</v>
       </c>
       <c r="H287">
         <v>1540</v>
@@ -41927,7 +41927,7 @@
         <v>0.66</v>
       </c>
       <c r="G288">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H288">
         <v>1540</v>
@@ -41980,7 +41980,7 @@
         <v>0.66</v>
       </c>
       <c r="G289">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H289">
         <v>1540</v>
@@ -42033,7 +42033,7 @@
         <v>0.66</v>
       </c>
       <c r="G290">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H290">
         <v>1540</v>
@@ -42086,7 +42086,7 @@
         <v>0.66</v>
       </c>
       <c r="G291">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H291">
         <v>1540</v>
@@ -42139,7 +42139,7 @@
         <v>0.66</v>
       </c>
       <c r="G292">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H292">
         <v>1540</v>
@@ -42192,7 +42192,7 @@
         <v>0.66</v>
       </c>
       <c r="G293">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H293">
         <v>1540</v>
@@ -42245,7 +42245,7 @@
         <v>0.66</v>
       </c>
       <c r="G294">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H294">
         <v>1540</v>
@@ -42298,7 +42298,7 @@
         <v>0.66</v>
       </c>
       <c r="G295">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H295">
         <v>1540</v>
@@ -42351,7 +42351,7 @@
         <v>0.66</v>
       </c>
       <c r="G296">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H296">
         <v>1540</v>
@@ -42404,7 +42404,7 @@
         <v>0.8</v>
       </c>
       <c r="G297">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H297">
         <v>1540</v>
@@ -42457,7 +42457,7 @@
         <v>0.66</v>
       </c>
       <c r="G298">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H298">
         <v>1540</v>
@@ -42510,7 +42510,7 @@
         <v>0.66</v>
       </c>
       <c r="G299">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H299">
         <v>1540</v>
@@ -42563,7 +42563,7 @@
         <v>0.66</v>
       </c>
       <c r="G300">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H300">
         <v>1540</v>
@@ -42616,7 +42616,7 @@
         <v>0.66</v>
       </c>
       <c r="G301">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H301">
         <v>1540</v>
@@ -42669,7 +42669,7 @@
         <v>0.8</v>
       </c>
       <c r="G302">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H302">
         <v>1540</v>
@@ -42722,7 +42722,7 @@
         <v>0.8</v>
       </c>
       <c r="G303">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H303">
         <v>1540</v>
@@ -42775,7 +42775,7 @@
         <v>0.8</v>
       </c>
       <c r="G304">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H304">
         <v>1540</v>
@@ -42828,7 +42828,7 @@
         <v>0.6</v>
       </c>
       <c r="G305">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H305">
         <v>1540</v>
@@ -42881,7 +42881,7 @@
         <v>0.6</v>
       </c>
       <c r="G306">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H306">
         <v>1540</v>
@@ -42934,7 +42934,7 @@
         <v>0.68500000000000005</v>
       </c>
       <c r="G307">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H307">
         <v>1540</v>
@@ -42987,7 +42987,7 @@
         <v>0.68500000000000005</v>
       </c>
       <c r="G308">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H308">
         <v>1540</v>
@@ -43040,7 +43040,7 @@
         <v>0.7</v>
       </c>
       <c r="G309">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H309">
         <v>1540</v>
@@ -43093,7 +43093,7 @@
         <v>0.7</v>
       </c>
       <c r="G310">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H310">
         <v>1540</v>
@@ -43146,7 +43146,7 @@
         <v>0.8</v>
       </c>
       <c r="G311">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H311">
         <v>1540</v>
@@ -43199,7 +43199,7 @@
         <v>0.8</v>
       </c>
       <c r="G312">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H312">
         <v>1540</v>
@@ -43252,7 +43252,7 @@
         <v>0.66</v>
       </c>
       <c r="G313">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H313">
         <v>1540</v>
@@ -43305,7 +43305,7 @@
         <v>0.66</v>
       </c>
       <c r="G314">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H314">
         <v>1540</v>
@@ -43358,7 +43358,7 @@
         <v>0.66</v>
       </c>
       <c r="G315">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H315">
         <v>1540</v>
@@ -43411,7 +43411,7 @@
         <v>0.66</v>
       </c>
       <c r="G316">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H316">
         <v>1540</v>
@@ -43464,7 +43464,7 @@
         <v>0.66</v>
       </c>
       <c r="G317">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H317">
         <v>1540</v>
@@ -43517,7 +43517,7 @@
         <v>0.66</v>
       </c>
       <c r="G318">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H318">
         <v>1540</v>
@@ -43570,7 +43570,7 @@
         <v>0.66</v>
       </c>
       <c r="G319">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H319">
         <v>1540</v>
@@ -43623,7 +43623,7 @@
         <v>0.66</v>
       </c>
       <c r="G320">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H320">
         <v>1540</v>
@@ -43676,7 +43676,7 @@
         <v>0.66</v>
       </c>
       <c r="G321">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H321">
         <v>1540</v>
@@ -43729,7 +43729,7 @@
         <v>0.66</v>
       </c>
       <c r="G322">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H322">
         <v>1540</v>
@@ -43782,7 +43782,7 @@
         <v>0.66</v>
       </c>
       <c r="G323">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H323">
         <v>1540</v>
@@ -43835,7 +43835,7 @@
         <v>0.66</v>
       </c>
       <c r="G324">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H324">
         <v>1540</v>
@@ -43888,7 +43888,7 @@
         <v>0.66</v>
       </c>
       <c r="G325">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H325">
         <v>1540</v>
@@ -43941,7 +43941,7 @@
         <v>0.66</v>
       </c>
       <c r="G326">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H326">
         <v>1540</v>
@@ -43994,7 +43994,7 @@
         <v>0.8</v>
       </c>
       <c r="G327">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999994</v>
       </c>
       <c r="H327">
         <v>1540</v>
@@ -44047,7 +44047,7 @@
         <v>0.8</v>
       </c>
       <c r="G328">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999994</v>
       </c>
       <c r="H328">
         <v>1540</v>
@@ -44100,7 +44100,7 @@
         <v>0.8</v>
       </c>
       <c r="G329">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H329">
         <v>1540</v>
@@ -44153,7 +44153,7 @@
         <v>0.66</v>
       </c>
       <c r="G330">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H330">
         <v>1540</v>
@@ -44206,7 +44206,7 @@
         <v>0.66</v>
       </c>
       <c r="G331">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H331">
         <v>1540</v>
@@ -44259,7 +44259,7 @@
         <v>0.66</v>
       </c>
       <c r="G332">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H332">
         <v>1540</v>
@@ -44312,7 +44312,7 @@
         <v>0.66</v>
       </c>
       <c r="G333">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H333">
         <v>1540</v>
@@ -44365,7 +44365,7 @@
         <v>0.66</v>
       </c>
       <c r="G334">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H334">
         <v>1540</v>
@@ -44418,7 +44418,7 @@
         <v>0.66</v>
       </c>
       <c r="G335">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H335">
         <v>1540</v>
@@ -44471,7 +44471,7 @@
         <v>0.66</v>
       </c>
       <c r="G336">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H336">
         <v>1540</v>
@@ -44524,7 +44524,7 @@
         <v>0.8</v>
       </c>
       <c r="G337">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999994</v>
       </c>
       <c r="H337">
         <v>1540</v>
@@ -44577,7 +44577,7 @@
         <v>0.8</v>
       </c>
       <c r="G338">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999994</v>
       </c>
       <c r="H338">
         <v>1540</v>
@@ -44630,7 +44630,7 @@
         <v>0.8</v>
       </c>
       <c r="G339">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999994</v>
       </c>
       <c r="H339">
         <v>1540</v>
@@ -44683,7 +44683,7 @@
         <v>0.8</v>
       </c>
       <c r="G340">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999994</v>
       </c>
       <c r="H340">
         <v>1540</v>
@@ -44736,7 +44736,7 @@
         <v>0.8</v>
       </c>
       <c r="G341">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999994</v>
       </c>
       <c r="H341">
         <v>1540</v>
@@ -44789,7 +44789,7 @@
         <v>0.66</v>
       </c>
       <c r="G342">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H342">
         <v>1540</v>
@@ -44842,7 +44842,7 @@
         <v>0.66</v>
       </c>
       <c r="G343">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H343">
         <v>1540</v>
@@ -44895,7 +44895,7 @@
         <v>0.66</v>
       </c>
       <c r="G344">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H344">
         <v>1540</v>
@@ -44948,7 +44948,7 @@
         <v>0.66</v>
       </c>
       <c r="G345">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H345">
         <v>1540</v>
@@ -45001,7 +45001,7 @@
         <v>0.66</v>
       </c>
       <c r="G346">
-        <v>0.39839999999999992</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H346">
         <v>1540</v>
@@ -45054,7 +45054,7 @@
         <v>0.66</v>
       </c>
       <c r="G347">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H347">
         <v>1540</v>
@@ -45107,7 +45107,7 @@
         <v>0.66</v>
       </c>
       <c r="G348">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H348">
         <v>1540</v>
@@ -45160,7 +45160,7 @@
         <v>0.6</v>
       </c>
       <c r="G349">
-        <v>0.37919999999999998</v>
+        <v>0.39057599999999998</v>
       </c>
       <c r="H349">
         <v>1540</v>
@@ -45213,7 +45213,7 @@
         <v>0.6</v>
       </c>
       <c r="G350">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999999</v>
       </c>
       <c r="H350">
         <v>1540</v>
@@ -45266,7 +45266,7 @@
         <v>0.8</v>
       </c>
       <c r="G351">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H351">
         <v>1540</v>
@@ -45319,7 +45319,7 @@
         <v>0.8</v>
       </c>
       <c r="G352">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H352">
         <v>1540</v>
@@ -45372,7 +45372,7 @@
         <v>0.8</v>
       </c>
       <c r="G353">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999994</v>
       </c>
       <c r="H353">
         <v>1540</v>
@@ -45425,7 +45425,7 @@
         <v>0.8</v>
       </c>
       <c r="G354">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H354">
         <v>1540</v>
@@ -45478,7 +45478,7 @@
         <v>0.8</v>
       </c>
       <c r="G355">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H355">
         <v>1540</v>
@@ -45531,7 +45531,7 @@
         <v>0.8</v>
       </c>
       <c r="G356">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H356">
         <v>1540</v>
@@ -45584,7 +45584,7 @@
         <v>0.8</v>
       </c>
       <c r="G357">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H357">
         <v>1540</v>
@@ -45637,7 +45637,7 @@
         <v>0.8</v>
       </c>
       <c r="G358">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H358">
         <v>1540</v>
@@ -45690,7 +45690,7 @@
         <v>0.8</v>
       </c>
       <c r="G359">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999994</v>
       </c>
       <c r="H359">
         <v>1540</v>
@@ -45743,7 +45743,7 @@
         <v>0.8</v>
       </c>
       <c r="G360">
-        <v>0.39839999999999998</v>
+        <v>0.41035199999999994</v>
       </c>
       <c r="H360">
         <v>1540</v>
@@ -45796,7 +45796,7 @@
         <v>0.66</v>
       </c>
       <c r="G361">
-        <v>0.40799999999999997</v>
+        <v>0.42024</v>
       </c>
       <c r="H361">
         <v>1540</v>
@@ -45849,7 +45849,7 @@
         <v>0.66</v>
       </c>
       <c r="G362">
-        <v>0.41759999999999997</v>
+        <v>0.43012800000000001</v>
       </c>
       <c r="H362">
         <v>1680</v>
@@ -45902,7 +45902,7 @@
         <v>0.66</v>
       </c>
       <c r="G363">
-        <v>0.41759999999999997</v>
+        <v>0.43012800000000001</v>
       </c>
       <c r="H363">
         <v>1680</v>
@@ -45955,7 +45955,7 @@
         <v>0.8</v>
       </c>
       <c r="G364">
-        <v>0.42719999999999997</v>
+        <v>0.44001599999999996</v>
       </c>
       <c r="H364">
         <v>1680</v>
@@ -46008,7 +46008,7 @@
         <v>0.8</v>
       </c>
       <c r="G365">
-        <v>0.42719999999999997</v>
+        <v>0.44001599999999996</v>
       </c>
       <c r="H365">
         <v>1680</v>
@@ -46061,7 +46061,7 @@
         <v>0.66</v>
       </c>
       <c r="G366">
-        <v>0.42720000000000002</v>
+        <v>0.44001599999999996</v>
       </c>
       <c r="H366">
         <v>1680</v>
@@ -46114,7 +46114,7 @@
         <v>0.66</v>
       </c>
       <c r="G367">
-        <v>0.42720000000000002</v>
+        <v>0.44001599999999996</v>
       </c>
       <c r="H367">
         <v>1680</v>
@@ -46167,7 +46167,7 @@
         <v>0.8</v>
       </c>
       <c r="G368">
-        <v>0.42719999999999997</v>
+        <v>0.44001599999999996</v>
       </c>
       <c r="H368">
         <v>1680</v>
@@ -46220,7 +46220,7 @@
         <v>0.8</v>
       </c>
       <c r="G369">
-        <v>0.42719999999999997</v>
+        <v>0.44001599999999996</v>
       </c>
       <c r="H369">
         <v>1680</v>
@@ -46273,7 +46273,7 @@
         <v>0.66</v>
       </c>
       <c r="G370">
-        <v>0.42720000000000002</v>
+        <v>0.44001599999999996</v>
       </c>
       <c r="H370">
         <v>1680</v>
@@ -46326,7 +46326,7 @@
         <v>0.66</v>
       </c>
       <c r="G371">
-        <v>0.42720000000000002</v>
+        <v>0.44001599999999996</v>
       </c>
       <c r="H371">
         <v>1680</v>
@@ -46379,7 +46379,7 @@
         <v>0.8</v>
       </c>
       <c r="G372">
-        <v>0.42719999999999997</v>
+        <v>0.44001599999999996</v>
       </c>
       <c r="H372">
         <v>1680</v>
@@ -46432,7 +46432,7 @@
         <v>0.8</v>
       </c>
       <c r="G373">
-        <v>0.42719999999999997</v>
+        <v>0.44001599999999996</v>
       </c>
       <c r="H373">
         <v>1680</v>
@@ -61287,7 +61287,7 @@
         <v>33</v>
       </c>
       <c r="L653">
-        <v>0.23343939125216409</v>
+        <v>0.23343939125216406</v>
       </c>
       <c r="N653" t="s">
         <v>723</v>
@@ -68646,7 +68646,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L833">
-        <v>0.27346342622727221</v>
+        <v>0.2734634262272721</v>
       </c>
     </row>
     <row r="834" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_IND/vt_vervestacks_IND_v1.xlsx
+++ b/VerveStacks_IND/vt_vervestacks_IND_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73C8E89E-71B5-4D1B-B515-4EC4429434F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4BE78B0-E6F8-4465-8E42-C922C1B9841D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C3F88FAF-1EB9-48D3-83D3-E31C948607D1}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E3D0FAC9-0E0F-40C2-B2DC-2BC72E1E8E2A}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -6458,7 +6458,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA1A9257-0EF1-4AF3-8856-4D8ADABE481E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB71727B-F9F3-4039-B7FE-F6110F9A6767}">
   <dimension ref="B9:T414"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27161,7 +27161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03C7AF13-6177-43E6-A78A-D7CF0EC70912}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C90A2A7-0CED-42D3-BDD4-4207D513BC0F}">
   <dimension ref="B9:T905"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -68646,7 +68646,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L833">
-        <v>0.2734634262272721</v>
+        <v>0.27346342622727221</v>
       </c>
     </row>
     <row r="834" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_IND/vt_vervestacks_IND_v1.xlsx
+++ b/VerveStacks_IND/vt_vervestacks_IND_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4BE78B0-E6F8-4465-8E42-C922C1B9841D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8CE68F1-CD73-40A7-8DD0-E29A5374AA61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E3D0FAC9-0E0F-40C2-B2DC-2BC72E1E8E2A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F582E8AE-6985-4E64-B7EF-A1C174A7AF93}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -6458,7 +6458,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB71727B-F9F3-4039-B7FE-F6110F9A6767}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E40E080-8D12-440F-9B01-C59A4D6FB761}">
   <dimension ref="B9:T414"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27161,7 +27161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C90A2A7-0CED-42D3-BDD4-4207D513BC0F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F72DC0BA-3EE9-442E-AEBB-0FCC8DD31132}">
   <dimension ref="B9:T905"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -61287,7 +61287,7 @@
         <v>33</v>
       </c>
       <c r="L653">
-        <v>0.23343939125216406</v>
+        <v>0.23343939125216409</v>
       </c>
       <c r="N653" t="s">
         <v>723</v>
